--- a/assets/Mangas.xlsx
+++ b/assets/Mangas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nahue\Desktop\proyectos\mangas\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B6F8B2-C30C-46AC-ADA9-E195FB8CC278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414E13CF-7005-4D23-9521-1F671A165925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="335">
   <si>
     <t>Estado</t>
   </si>
@@ -873,9 +873,6 @@
     <t>Hooky - 2 &amp; 3</t>
   </si>
   <si>
-    <t>Rooster Fighter - 5 al 7</t>
-  </si>
-  <si>
     <t>Un Extraño en Primavera - 1 al 5</t>
   </si>
   <si>
@@ -906,9 +903,6 @@
     <t>Obaru</t>
   </si>
   <si>
-    <t>Hikaru Ga Shinda Natsu - 2 al 5</t>
-  </si>
-  <si>
     <t>Los Pecados de la Familia Ichinose</t>
   </si>
   <si>
@@ -972,18 +966,9 @@
     <t>Spy x Family - 11 al 15</t>
   </si>
   <si>
-    <t>Gachiakuta - 2 al 10</t>
-  </si>
-  <si>
-    <t>Elden Ring - 1 al 6</t>
-  </si>
-  <si>
     <t>El Morador de las Tinieblas</t>
   </si>
   <si>
-    <t>Girls´ Last Tour - 1</t>
-  </si>
-  <si>
     <t>Tsukumizu</t>
   </si>
   <si>
@@ -996,24 +981,6 @@
     <t>Adabana - 1 al 3</t>
   </si>
   <si>
-    <t>Blue Lock - 13 al 33</t>
-  </si>
-  <si>
-    <t>Blue Lock : Episode Nagi - 1 al 7</t>
-  </si>
-  <si>
-    <t>Re:Zero - 13 al 21</t>
-  </si>
-  <si>
-    <t>Sakamoto Days - 3 al 17</t>
-  </si>
-  <si>
-    <t>Dandadan - 8 al 18</t>
-  </si>
-  <si>
-    <t>Solo Leveling - 4 al 11</t>
-  </si>
-  <si>
     <t>La Tierra de las Gemas - 3 al 9</t>
   </si>
   <si>
@@ -1033,6 +1000,42 @@
   </si>
   <si>
     <t>Shinnosuke Kanazawa</t>
+  </si>
+  <si>
+    <t>Girls´ Last Tour - 1 al 3</t>
+  </si>
+  <si>
+    <t>Solo Leveling - 4 al 12</t>
+  </si>
+  <si>
+    <t>Re:Zero - 13 al 23</t>
+  </si>
+  <si>
+    <t>Hikaru Ga Shinda Natsu - 2 al 6</t>
+  </si>
+  <si>
+    <t>Elden Ring - 1 al 7</t>
+  </si>
+  <si>
+    <t>Rooster Fighter - 5 al 9</t>
+  </si>
+  <si>
+    <t>Sakamoto Days - 3 al 18</t>
+  </si>
+  <si>
+    <t>Gachiakuta - 2 al 12</t>
+  </si>
+  <si>
+    <t>Dandadan - 8 al 20</t>
+  </si>
+  <si>
+    <t>Blue Lock - 13 al 35</t>
+  </si>
+  <si>
+    <t>Blue Lock : Episode Nagi - 1 al 8</t>
+  </si>
+  <si>
+    <t>Danganronpa 2</t>
   </si>
 </sst>
 </file>
@@ -1851,22 +1854,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.85546875" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.86328125" customWidth="1"/>
+    <col min="4" max="4" width="6.86328125" customWidth="1"/>
+    <col min="5" max="5" width="13.1328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.7109375" customWidth="1"/>
+    <col min="7" max="7" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.73046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.73046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.73046875" customWidth="1"/>
     <col min="11" max="11" width="52" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>271</v>
       </c>
@@ -1901,7 +1904,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
@@ -1921,7 +1924,7 @@
         <v>13</v>
       </c>
       <c r="G2" s="7">
-        <f t="shared" ref="G2:G133" si="0">D2*E2</f>
+        <f t="shared" ref="G2:G134" si="0">D2*E2</f>
         <v>253000</v>
       </c>
       <c r="H2" s="44" t="s">
@@ -1934,10 +1937,10 @@
         <v>14</v>
       </c>
       <c r="K2" s="41" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -1970,10 +1973,10 @@
         <v>14</v>
       </c>
       <c r="K3" s="41" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
@@ -2009,7 +2012,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
@@ -2020,7 +2023,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E5" s="7">
         <v>11000</v>
@@ -2030,7 +2033,7 @@
       </c>
       <c r="G5" s="7">
         <f t="shared" si="0"/>
-        <v>231000</v>
+        <v>253000</v>
       </c>
       <c r="H5" s="44" t="s">
         <v>273</v>
@@ -2042,10 +2045,10 @@
         <v>20</v>
       </c>
       <c r="K5" s="41" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
@@ -2078,10 +2081,10 @@
         <v>23</v>
       </c>
       <c r="K6" s="41" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
@@ -2117,7 +2120,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
@@ -2128,7 +2131,7 @@
         <v>30</v>
       </c>
       <c r="D8" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" s="7">
         <v>12500</v>
@@ -2138,7 +2141,7 @@
       </c>
       <c r="G8" s="7">
         <f t="shared" si="0"/>
-        <v>62500</v>
+        <v>75000</v>
       </c>
       <c r="H8" s="44" t="s">
         <v>273</v>
@@ -2150,10 +2153,10 @@
         <v>31</v>
       </c>
       <c r="K8" s="41" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -2164,7 +2167,7 @@
         <v>90</v>
       </c>
       <c r="D9" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" s="7">
         <v>11000</v>
@@ -2174,7 +2177,7 @@
       </c>
       <c r="G9" s="7">
         <f>D9*E9</f>
-        <v>66000</v>
+        <v>77000</v>
       </c>
       <c r="H9" s="44" t="s">
         <v>273</v>
@@ -2186,10 +2189,10 @@
         <v>92</v>
       </c>
       <c r="K9" s="41" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A10" s="4" t="s">
         <v>10</v>
       </c>
@@ -2197,7 +2200,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D10" s="11">
         <v>2</v>
@@ -2216,16 +2219,16 @@
         <v>273</v>
       </c>
       <c r="I10" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="K10" s="41" t="s">
         <v>304</v>
       </c>
-      <c r="J10" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="K10" s="41" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
@@ -2233,7 +2236,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="D11" s="11">
         <v>1</v>
@@ -2252,16 +2255,16 @@
         <v>273</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="K11" s="41" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -2269,7 +2272,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="D12" s="11">
         <v>1</v>
@@ -2288,16 +2291,16 @@
         <v>273</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="K12" s="41" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A13" s="4" t="s">
         <v>10</v>
       </c>
@@ -2330,10 +2333,10 @@
         <v>34</v>
       </c>
       <c r="K13" s="41" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
@@ -2344,17 +2347,17 @@
         <v>39</v>
       </c>
       <c r="D14" s="11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E14" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G14" s="7">
         <f t="shared" si="0"/>
-        <v>69300</v>
+        <v>94500</v>
       </c>
       <c r="H14" s="44" t="s">
         <v>273</v>
@@ -2366,10 +2369,10 @@
         <v>40</v>
       </c>
       <c r="K14" s="41" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A15" s="4" t="s">
         <v>10</v>
       </c>
@@ -2383,14 +2386,14 @@
         <v>5</v>
       </c>
       <c r="E15" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G15" s="7">
         <f t="shared" ref="G15" si="1">D15*E15</f>
-        <v>49500</v>
+        <v>52500</v>
       </c>
       <c r="H15" s="44" t="s">
         <v>273</v>
@@ -2402,46 +2405,46 @@
         <v>44</v>
       </c>
       <c r="K15" s="41" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A16" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="D16" s="11">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="D16" s="6">
+        <v>15</v>
       </c>
       <c r="E16" s="7">
-        <v>16900</v>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>210</v>
+        <v>9500</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="G16" s="7">
-        <f t="shared" ref="G16" si="2">D16*E16</f>
-        <v>16900</v>
+        <f t="shared" si="0"/>
+        <v>142500</v>
       </c>
       <c r="H16" s="44" t="s">
         <v>273</v>
       </c>
-      <c r="I16" s="16" t="s">
-        <v>317</v>
-      </c>
-      <c r="J16" s="16" t="s">
-        <v>317</v>
+      <c r="I16" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="K16" s="41" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A17" s="4" t="s">
         <v>10</v>
       </c>
@@ -2449,35 +2452,35 @@
         <v>35</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="6">
-        <v>15</v>
+        <v>48</v>
+      </c>
+      <c r="D17" s="11">
+        <v>35</v>
       </c>
       <c r="E17" s="7">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G17" s="7">
-        <f t="shared" si="0"/>
-        <v>133500</v>
+        <f t="shared" ref="G17" si="2">D17*E17</f>
+        <v>332500</v>
       </c>
       <c r="H17" s="44" t="s">
         <v>273</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K17" s="41" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A18" s="4" t="s">
         <v>10</v>
       </c>
@@ -2485,20 +2488,20 @@
         <v>35</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>48</v>
+        <v>264</v>
       </c>
       <c r="D18" s="11">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E18" s="7">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G18" s="7">
-        <f t="shared" ref="G18" si="3">D18*E18</f>
-        <v>293700</v>
+        <f t="shared" si="0"/>
+        <v>76000</v>
       </c>
       <c r="H18" s="44" t="s">
         <v>273</v>
@@ -2510,10 +2513,10 @@
         <v>50</v>
       </c>
       <c r="K18" s="41" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A19" s="4" t="s">
         <v>10</v>
       </c>
@@ -2521,35 +2524,32 @@
         <v>35</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="D19" s="11">
-        <v>7</v>
+        <v>51</v>
+      </c>
+      <c r="D19" s="6">
+        <v>21</v>
       </c>
       <c r="E19" s="7">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G19" s="7">
         <f t="shared" si="0"/>
-        <v>62300</v>
+        <v>199500</v>
       </c>
       <c r="H19" s="44" t="s">
         <v>273</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K19" s="41" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A20" s="4" t="s">
         <v>10</v>
       </c>
@@ -2557,32 +2557,35 @@
         <v>35</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D20" s="6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E20" s="7">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G20" s="7">
         <f t="shared" si="0"/>
-        <v>178000</v>
+        <v>171000</v>
       </c>
       <c r="H20" s="44" t="s">
         <v>273</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="K20" s="41" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="4" t="s">
         <v>10</v>
       </c>
@@ -2590,35 +2593,35 @@
         <v>35</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="6">
-        <v>17</v>
+        <v>57</v>
+      </c>
+      <c r="D21" s="11">
+        <v>20</v>
       </c>
       <c r="E21" s="7">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G21" s="7">
         <f t="shared" si="0"/>
-        <v>151300</v>
+        <v>190000</v>
       </c>
       <c r="H21" s="44" t="s">
         <v>273</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K21" s="41" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="4" t="s">
         <v>10</v>
       </c>
@@ -2626,35 +2629,35 @@
         <v>35</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D22" s="11">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E22" s="7">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G22" s="7">
         <f t="shared" si="0"/>
-        <v>160200</v>
+        <v>114000</v>
       </c>
       <c r="H22" s="44" t="s">
         <v>273</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K22" s="41" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
         <v>10</v>
       </c>
@@ -2662,35 +2665,35 @@
         <v>35</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="11">
-        <v>10</v>
+        <v>61</v>
+      </c>
+      <c r="D23" s="6">
+        <v>3</v>
       </c>
       <c r="E23" s="7">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G23" s="7">
-        <f t="shared" si="0"/>
-        <v>89000</v>
+        <f t="shared" ref="G23" si="3">D23*E23</f>
+        <v>28500</v>
       </c>
       <c r="H23" s="44" t="s">
         <v>273</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K23" s="41" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
         <v>10</v>
       </c>
@@ -2698,35 +2701,35 @@
         <v>35</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>61</v>
+        <v>290</v>
       </c>
       <c r="D24" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" s="7">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G24" s="7">
-        <f t="shared" ref="G24" si="4">D24*E24</f>
-        <v>26700</v>
+        <f t="shared" si="0"/>
+        <v>19000</v>
       </c>
       <c r="H24" s="44" t="s">
         <v>273</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="K24" s="41" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
         <v>10</v>
       </c>
@@ -2734,35 +2737,35 @@
         <v>35</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>292</v>
+        <v>64</v>
       </c>
       <c r="D25" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E25" s="7">
-        <v>8900</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>46</v>
+        <v>27000</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>65</v>
       </c>
       <c r="G25" s="7">
         <f t="shared" si="0"/>
-        <v>17800</v>
+        <v>324000</v>
       </c>
       <c r="H25" s="44" t="s">
         <v>273</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="K25" s="41" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="4" t="s">
         <v>10</v>
       </c>
@@ -2770,176 +2773,176 @@
         <v>35</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D26" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E26" s="7">
-        <v>25900</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>65</v>
+        <v>12900</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="G26" s="7">
         <f t="shared" si="0"/>
-        <v>284900</v>
+        <v>167700</v>
       </c>
       <c r="H26" s="44" t="s">
         <v>273</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="K26" s="41" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B27" s="14" t="s">
-        <v>35</v>
+      <c r="B27" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D27" s="6">
+        <v>9</v>
+      </c>
+      <c r="E27" s="7">
+        <v>12000</v>
+      </c>
+      <c r="F27" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="7">
-        <v>10900</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>33</v>
-      </c>
       <c r="G27" s="7">
         <f t="shared" si="0"/>
-        <v>141700</v>
+        <v>108000</v>
       </c>
       <c r="H27" s="44" t="s">
         <v>273</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="K27" s="41" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>70</v>
+      <c r="B28" s="18" t="s">
+        <v>73</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D28" s="6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E28" s="7">
-        <v>12000</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>13</v>
+        <v>37000</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="G28" s="7">
         <f t="shared" si="0"/>
-        <v>108000</v>
-      </c>
-      <c r="H28" s="44" t="s">
-        <v>273</v>
+        <v>74000</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>182</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="K28" s="41" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>73</v>
+      <c r="B29" s="19" t="s">
+        <v>79</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D29" s="6">
         <v>2</v>
       </c>
       <c r="E29" s="7">
-        <v>37000</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>33</v>
+        <v>32000</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>65</v>
       </c>
       <c r="G29" s="7">
         <f t="shared" si="0"/>
-        <v>74000</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>182</v>
+        <v>64000</v>
+      </c>
+      <c r="H29" s="44" t="s">
+        <v>273</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K29" s="41" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>79</v>
+        <v>278</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D30" s="6">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="E30" s="7">
-        <v>32000</v>
-      </c>
-      <c r="F30" s="17" t="s">
-        <v>65</v>
+        <v>12500</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="G30" s="7">
         <f t="shared" si="0"/>
-        <v>64000</v>
-      </c>
-      <c r="H30" s="44" t="s">
-        <v>273</v>
+        <v>350000</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>182</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="K30" s="41" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="K30" s="42" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="20" t="s">
         <v>82</v>
       </c>
@@ -2947,35 +2950,32 @@
         <v>11</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="D31" s="6">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E31" s="7">
-        <v>12500</v>
+        <v>11000</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G31" s="7">
-        <f t="shared" si="0"/>
-        <v>350000</v>
+        <f>D31*E31</f>
+        <v>143000</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="K31" s="42" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="20" t="s">
         <v>82</v>
       </c>
@@ -2983,32 +2983,32 @@
         <v>11</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="D32" s="6">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E32" s="7">
-        <v>11000</v>
+        <v>10500</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G32" s="7">
-        <f>D32*E32</f>
-        <v>143000</v>
+        <f t="shared" si="0"/>
+        <v>21000</v>
       </c>
       <c r="H32" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="20" t="s">
         <v>82</v>
       </c>
@@ -3016,32 +3016,35 @@
         <v>11</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D33" s="6">
-        <v>2</v>
+        <v>87</v>
+      </c>
+      <c r="D33" s="11">
+        <v>9</v>
       </c>
       <c r="E33" s="7">
-        <v>10500</v>
+        <v>12500</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G33" s="7">
         <f t="shared" si="0"/>
-        <v>21000</v>
+        <v>112500</v>
       </c>
       <c r="H33" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="K33" s="41" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="20" t="s">
         <v>82</v>
       </c>
@@ -3049,10 +3052,10 @@
         <v>11</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D34" s="11">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E34" s="7">
         <v>12500</v>
@@ -3062,58 +3065,55 @@
       </c>
       <c r="G34" s="7">
         <f t="shared" si="0"/>
-        <v>112500</v>
+        <v>275000</v>
       </c>
       <c r="H34" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K34" s="41" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>11</v>
+      <c r="B35" s="14" t="s">
+        <v>35</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D35" s="11">
-        <v>22</v>
+        <v>97</v>
+      </c>
+      <c r="D35" s="6">
+        <v>23</v>
       </c>
       <c r="E35" s="7">
-        <v>12500</v>
+        <v>9500</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="G35" s="7">
         <f t="shared" si="0"/>
-        <v>275000</v>
+        <v>218500</v>
       </c>
       <c r="H35" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="K35" s="41" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="20" t="s">
         <v>82</v>
       </c>
@@ -3121,32 +3121,32 @@
         <v>35</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D36" s="6">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E36" s="7">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G36" s="7">
         <f t="shared" si="0"/>
-        <v>204700</v>
+        <v>114000</v>
       </c>
       <c r="H36" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="20" t="s">
         <v>82</v>
       </c>
@@ -3154,32 +3154,35 @@
         <v>35</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D37" s="6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E37" s="7">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G37" s="7">
         <f t="shared" si="0"/>
-        <v>106800</v>
+        <v>76000</v>
       </c>
       <c r="H37" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="K37" s="41" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="20" t="s">
         <v>82</v>
       </c>
@@ -3187,71 +3190,71 @@
         <v>35</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="D38" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E38" s="7">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G38" s="7">
-        <f t="shared" si="0"/>
-        <v>71200</v>
+        <f>D38*E38</f>
+        <v>104500</v>
       </c>
       <c r="H38" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K38" s="41" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="15" t="s">
         <v>35</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D39" s="6">
-        <v>11</v>
+        <v>313</v>
+      </c>
+      <c r="D39" s="11">
+        <v>3</v>
       </c>
       <c r="E39" s="7">
-        <v>8900</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>46</v>
+        <v>17900</v>
+      </c>
+      <c r="F39" s="28" t="s">
+        <v>210</v>
       </c>
       <c r="G39" s="7">
         <f>D39*E39</f>
-        <v>97900</v>
+        <v>53700</v>
       </c>
       <c r="H39" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="I39" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="J39" s="10" t="s">
-        <v>56</v>
+      <c r="I39" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="J39" s="16" t="s">
+        <v>312</v>
       </c>
       <c r="K39" s="41" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="20" t="s">
         <v>82</v>
       </c>
@@ -3265,14 +3268,14 @@
         <v>12</v>
       </c>
       <c r="E40" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G40" s="7">
         <f>D40*E40</f>
-        <v>118800</v>
+        <v>126000</v>
       </c>
       <c r="H40" s="13" t="s">
         <v>182</v>
@@ -3284,10 +3287,10 @@
         <v>42</v>
       </c>
       <c r="K40" s="41" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="20" t="s">
         <v>82</v>
       </c>
@@ -3301,14 +3304,14 @@
         <v>16</v>
       </c>
       <c r="E41" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G41" s="7">
         <f>D41*E41</f>
-        <v>158400</v>
+        <v>168000</v>
       </c>
       <c r="H41" s="13" t="s">
         <v>182</v>
@@ -3320,10 +3323,10 @@
         <v>38</v>
       </c>
       <c r="K41" s="41" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="20" t="s">
         <v>82</v>
       </c>
@@ -3337,14 +3340,14 @@
         <v>2</v>
       </c>
       <c r="E42" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G42" s="7">
         <f t="shared" si="0"/>
-        <v>19800</v>
+        <v>21000</v>
       </c>
       <c r="H42" s="13" t="s">
         <v>182</v>
@@ -3359,7 +3362,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="20" t="s">
         <v>82</v>
       </c>
@@ -3367,35 +3370,35 @@
         <v>35</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D43" s="11">
         <v>3</v>
       </c>
       <c r="E43" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G43" s="7">
         <f>D43*E43</f>
-        <v>29700</v>
+        <v>31500</v>
       </c>
       <c r="H43" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I43" s="16" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J43" s="16" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K43" s="41" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="20" t="s">
         <v>82</v>
       </c>
@@ -3409,14 +3412,14 @@
         <v>3</v>
       </c>
       <c r="E44" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G44" s="7">
         <f t="shared" si="0"/>
-        <v>29700</v>
+        <v>31500</v>
       </c>
       <c r="H44" s="13" t="s">
         <v>182</v>
@@ -3431,7 +3434,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="20" t="s">
         <v>82</v>
       </c>
@@ -3445,14 +3448,14 @@
         <v>3</v>
       </c>
       <c r="E45" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G45" s="7">
         <f t="shared" si="0"/>
-        <v>29700</v>
+        <v>31500</v>
       </c>
       <c r="H45" s="13" t="s">
         <v>182</v>
@@ -3467,7 +3470,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="20" t="s">
         <v>82</v>
       </c>
@@ -3481,14 +3484,14 @@
         <v>13</v>
       </c>
       <c r="E46" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G46" s="7">
         <f t="shared" si="0"/>
-        <v>128700</v>
+        <v>136500</v>
       </c>
       <c r="H46" s="13" t="s">
         <v>182</v>
@@ -3500,7 +3503,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="20" t="s">
         <v>82</v>
       </c>
@@ -3514,14 +3517,14 @@
         <v>8</v>
       </c>
       <c r="E47" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G47" s="7">
         <f t="shared" si="0"/>
-        <v>79200</v>
+        <v>84000</v>
       </c>
       <c r="H47" s="13" t="s">
         <v>182</v>
@@ -3533,7 +3536,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="20" t="s">
         <v>82</v>
       </c>
@@ -3547,14 +3550,14 @@
         <v>4</v>
       </c>
       <c r="E48" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G48" s="7">
-        <f t="shared" si="0"/>
-        <v>39600</v>
+        <f t="shared" ref="G48" si="4">D48*E48</f>
+        <v>42000</v>
       </c>
       <c r="H48" s="13" t="s">
         <v>182</v>
@@ -3566,7 +3569,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="20" t="s">
         <v>82</v>
       </c>
@@ -3574,32 +3577,32 @@
         <v>35</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>119</v>
+        <v>334</v>
       </c>
       <c r="D49" s="6">
         <v>3</v>
       </c>
       <c r="E49" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G49" s="7">
         <f t="shared" si="0"/>
-        <v>29700</v>
+        <v>31500</v>
       </c>
       <c r="H49" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="20" t="s">
         <v>82</v>
       </c>
@@ -3607,20 +3610,20 @@
         <v>35</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D50" s="6">
         <v>3</v>
       </c>
       <c r="E50" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G50" s="7">
         <f t="shared" si="0"/>
-        <v>29700</v>
+        <v>31500</v>
       </c>
       <c r="H50" s="13" t="s">
         <v>182</v>
@@ -3632,7 +3635,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="20" t="s">
         <v>82</v>
       </c>
@@ -3640,20 +3643,20 @@
         <v>35</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D51" s="6">
         <v>3</v>
       </c>
       <c r="E51" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G51" s="7">
         <f t="shared" si="0"/>
-        <v>29700</v>
+        <v>31500</v>
       </c>
       <c r="H51" s="13" t="s">
         <v>182</v>
@@ -3665,7 +3668,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="20" t="s">
         <v>82</v>
       </c>
@@ -3673,20 +3676,20 @@
         <v>35</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D52" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G52" s="7">
-        <f t="shared" ref="G52" si="5">D52*E52</f>
-        <v>19800</v>
+        <f t="shared" si="0"/>
+        <v>31500</v>
       </c>
       <c r="H52" s="13" t="s">
         <v>182</v>
@@ -3695,10 +3698,10 @@
         <v>120</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="20" t="s">
         <v>82</v>
       </c>
@@ -3706,20 +3709,20 @@
         <v>35</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>275</v>
+        <v>124</v>
       </c>
       <c r="D53" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" s="7">
-        <v>8300</v>
+        <v>10500</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G53" s="7">
-        <f>D53*E53</f>
-        <v>24900</v>
+        <f t="shared" ref="G53" si="5">D53*E53</f>
+        <v>21000</v>
       </c>
       <c r="H53" s="13" t="s">
         <v>182</v>
@@ -3728,46 +3731,46 @@
         <v>120</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B54" s="18" t="s">
-        <v>73</v>
+      <c r="B54" s="14" t="s">
+        <v>35</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>126</v>
+        <v>275</v>
       </c>
       <c r="D54" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E54" s="7">
-        <v>14900</v>
+        <v>8300</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G54" s="7">
-        <f t="shared" si="0"/>
-        <v>59600</v>
+        <f>D54*E54</f>
+        <v>24900</v>
       </c>
       <c r="H54" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="K54" s="41" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="20" t="s">
         <v>82</v>
       </c>
@@ -3775,35 +3778,35 @@
         <v>73</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="D55" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E55" s="7">
-        <v>16600</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>33</v>
+        <v>17700</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="G55" s="7">
-        <f>D55*E55</f>
-        <v>33200</v>
+        <f t="shared" si="0"/>
+        <v>70800</v>
       </c>
       <c r="H55" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="K55" s="41" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="20" t="s">
         <v>82</v>
       </c>
@@ -3811,179 +3814,179 @@
         <v>73</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="D56" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E56" s="7">
-        <v>14100</v>
+        <v>18900</v>
       </c>
       <c r="F56" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G56" s="7">
-        <f t="shared" si="0"/>
-        <v>70500</v>
+        <f>D56*E56</f>
+        <v>37800</v>
       </c>
       <c r="H56" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="K56" s="41" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B57" s="21" t="s">
-        <v>132</v>
+      <c r="B57" s="18" t="s">
+        <v>73</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D57" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E57" s="7">
-        <v>12000</v>
+        <v>18800</v>
       </c>
       <c r="F57" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G57" s="7">
         <f t="shared" si="0"/>
-        <v>24000</v>
+        <v>94000</v>
       </c>
       <c r="H57" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="K57" s="41" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B58" s="34" t="s">
-        <v>257</v>
+      <c r="B58" s="21" t="s">
+        <v>132</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>298</v>
+        <v>133</v>
       </c>
       <c r="D58" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58" s="7">
-        <v>18900</v>
+        <v>12000</v>
       </c>
       <c r="F58" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G58" s="7">
-        <f>D58*E58</f>
-        <v>56700</v>
+        <f t="shared" si="0"/>
+        <v>24000</v>
       </c>
       <c r="H58" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>259</v>
+        <v>134</v>
       </c>
       <c r="J58" s="10" t="s">
-        <v>259</v>
+        <v>134</v>
       </c>
       <c r="K58" s="41" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B59" s="22" t="s">
-        <v>136</v>
+      <c r="B59" s="34" t="s">
+        <v>257</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>137</v>
+        <v>296</v>
       </c>
       <c r="D59" s="6">
         <v>3</v>
       </c>
       <c r="E59" s="7">
-        <v>13500</v>
+        <v>18900</v>
       </c>
       <c r="F59" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G59" s="7">
-        <f t="shared" si="0"/>
-        <v>40500</v>
+        <f>D59*E59</f>
+        <v>56700</v>
       </c>
       <c r="H59" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>138</v>
+        <v>259</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>138</v>
+        <v>259</v>
       </c>
       <c r="K59" s="41" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B60" s="23" t="s">
-        <v>140</v>
+      <c r="B60" s="22" t="s">
+        <v>136</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D60" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E60" s="7">
-        <v>11900</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>13</v>
+        <v>15000</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="G60" s="7">
         <f t="shared" si="0"/>
-        <v>59500</v>
+        <v>45000</v>
       </c>
       <c r="H60" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="K60" s="41" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="20" t="s">
         <v>82</v>
       </c>
@@ -3991,10 +3994,10 @@
         <v>140</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D61" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E61" s="7">
         <v>11900</v>
@@ -4004,55 +4007,55 @@
       </c>
       <c r="G61" s="7">
         <f t="shared" si="0"/>
-        <v>35700</v>
+        <v>59500</v>
       </c>
       <c r="H61" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K61" s="41" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B62" s="24" t="s">
-        <v>148</v>
+      <c r="B62" s="23" t="s">
+        <v>140</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D62" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" s="7">
-        <v>9000</v>
+        <v>11900</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G62" s="7">
         <f t="shared" si="0"/>
-        <v>18000</v>
+        <v>35700</v>
       </c>
       <c r="H62" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="20" t="s">
         <v>82</v>
       </c>
@@ -4060,7 +4063,7 @@
         <v>148</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D63" s="6">
         <v>2</v>
@@ -4069,7 +4072,7 @@
         <v>9000</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="G63" s="7">
         <f t="shared" si="0"/>
@@ -4079,49 +4082,49 @@
         <v>182</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K63" s="41" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>11</v>
+    <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B64" s="24" t="s">
+        <v>148</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D64" s="6">
         <v>2</v>
       </c>
       <c r="E64" s="7">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="G64" s="7">
         <f t="shared" si="0"/>
-        <v>24000</v>
-      </c>
-      <c r="H64" s="44" t="s">
-        <v>273</v>
+        <v>18000</v>
+      </c>
+      <c r="H64" s="13" t="s">
+        <v>182</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="25" t="s">
         <v>154</v>
       </c>
@@ -4129,32 +4132,32 @@
         <v>11</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D65" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" s="7">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G65" s="7">
         <f t="shared" si="0"/>
-        <v>11000</v>
-      </c>
-      <c r="H65" s="13" t="s">
-        <v>182</v>
+        <v>24000</v>
+      </c>
+      <c r="H65" s="44" t="s">
+        <v>273</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="25" t="s">
         <v>154</v>
       </c>
@@ -4162,65 +4165,65 @@
         <v>11</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D66" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E66" s="7">
-        <v>12500</v>
+        <v>11000</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G66" s="7">
         <f t="shared" si="0"/>
-        <v>37500</v>
+        <v>11000</v>
       </c>
       <c r="H66" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="B67" s="14" t="s">
-        <v>35</v>
+      <c r="B67" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D67" s="6">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E67" s="7">
-        <v>8900</v>
+        <v>12500</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="G67" s="7">
         <f t="shared" si="0"/>
-        <v>106800</v>
+        <v>37500</v>
       </c>
       <c r="H67" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J67" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="25" t="s">
         <v>154</v>
       </c>
@@ -4228,32 +4231,32 @@
         <v>35</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D68" s="6">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E68" s="7">
-        <v>17700</v>
+        <v>9500</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G68" s="7">
         <f t="shared" si="0"/>
-        <v>17700</v>
+        <v>114000</v>
       </c>
       <c r="H68" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J68" s="10" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="25" t="s">
         <v>154</v>
       </c>
@@ -4261,32 +4264,32 @@
         <v>35</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D69" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E69" s="7">
-        <v>8900</v>
+        <v>17700</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G69" s="7">
         <f t="shared" si="0"/>
-        <v>53400</v>
-      </c>
-      <c r="H69" s="44" t="s">
-        <v>273</v>
+        <v>17700</v>
+      </c>
+      <c r="H69" s="13" t="s">
+        <v>182</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="25" t="s">
         <v>154</v>
       </c>
@@ -4294,32 +4297,32 @@
         <v>35</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D70" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E70" s="7">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G70" s="7">
         <f t="shared" si="0"/>
-        <v>35600</v>
+        <v>57000</v>
       </c>
       <c r="H70" s="44" t="s">
         <v>273</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J70" s="10" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="25" t="s">
         <v>154</v>
       </c>
@@ -4327,32 +4330,32 @@
         <v>35</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D71" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E71" s="7">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G71" s="7">
         <f t="shared" si="0"/>
-        <v>44500</v>
+        <v>38000</v>
       </c>
       <c r="H71" s="44" t="s">
         <v>273</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J71" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="25" t="s">
         <v>154</v>
       </c>
@@ -4360,32 +4363,32 @@
         <v>35</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D72" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E72" s="7">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G72" s="7">
         <f t="shared" si="0"/>
-        <v>8900</v>
+        <v>47500</v>
       </c>
       <c r="H72" s="44" t="s">
         <v>273</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="25" t="s">
         <v>154</v>
       </c>
@@ -4393,32 +4396,32 @@
         <v>35</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D73" s="6">
         <v>1</v>
       </c>
       <c r="E73" s="7">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G73" s="7">
         <f t="shared" si="0"/>
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="H73" s="44" t="s">
         <v>273</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J73" s="10" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="25" t="s">
         <v>154</v>
       </c>
@@ -4426,32 +4429,32 @@
         <v>35</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D74" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E74" s="7">
-        <v>9900</v>
+        <v>9500</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="G74" s="7">
         <f t="shared" si="0"/>
-        <v>49500</v>
-      </c>
-      <c r="H74" s="13" t="s">
-        <v>182</v>
+        <v>9500</v>
+      </c>
+      <c r="H74" s="44" t="s">
+        <v>273</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J74" s="10" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="25" t="s">
         <v>154</v>
       </c>
@@ -4459,101 +4462,101 @@
         <v>35</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D75" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E75" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G75" s="7">
         <f t="shared" si="0"/>
-        <v>9900</v>
-      </c>
-      <c r="H75" s="44" t="s">
+        <v>52500</v>
+      </c>
+      <c r="H75" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="I75" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="J75" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A76" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D76" s="6">
+        <v>1</v>
+      </c>
+      <c r="E76" s="7">
+        <v>10500</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="7">
+        <f t="shared" si="0"/>
+        <v>10500</v>
+      </c>
+      <c r="H76" s="44" t="s">
         <v>273</v>
       </c>
-      <c r="I75" s="10" t="s">
+      <c r="I76" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="J75" s="10" t="s">
+      <c r="J76" s="10" t="s">
         <v>178</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="B76" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D76" s="11">
-        <v>1</v>
-      </c>
-      <c r="E76" s="7">
-        <v>18000</v>
-      </c>
-      <c r="F76" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="G76" s="7">
-        <f t="shared" si="0"/>
-        <v>18000</v>
-      </c>
-      <c r="H76" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="I76" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="J76" s="16" t="s">
-        <v>14</v>
       </c>
       <c r="K76" s="41" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B77" s="14" t="s">
-        <v>35</v>
+      <c r="B77" s="15" t="s">
+        <v>180</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="D77" s="6">
+        <v>181</v>
+      </c>
+      <c r="D77" s="11">
         <v>1</v>
       </c>
       <c r="E77" s="7">
-        <v>9900</v>
-      </c>
-      <c r="F77" s="8" t="s">
+        <v>18000</v>
+      </c>
+      <c r="F77" s="27" t="s">
         <v>13</v>
       </c>
       <c r="G77" s="7">
         <f t="shared" si="0"/>
-        <v>9900</v>
+        <v>18000</v>
       </c>
       <c r="H77" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="I77" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J77" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I77" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="J77" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="26" t="s">
         <v>179</v>
       </c>
@@ -4561,32 +4564,32 @@
         <v>35</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D78" s="6">
         <v>1</v>
       </c>
       <c r="E78" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G78" s="7">
         <f t="shared" si="0"/>
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="H78" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>185</v>
+        <v>38</v>
       </c>
       <c r="J78" s="10" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="26" t="s">
         <v>179</v>
       </c>
@@ -4594,32 +4597,32 @@
         <v>35</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D79" s="6">
         <v>1</v>
       </c>
       <c r="E79" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G79" s="7">
         <f t="shared" si="0"/>
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="H79" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>42</v>
+        <v>185</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="26" t="s">
         <v>179</v>
       </c>
@@ -4627,32 +4630,32 @@
         <v>35</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D80" s="6">
         <v>1</v>
       </c>
       <c r="E80" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G80" s="7">
         <f t="shared" si="0"/>
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="H80" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="26" t="s">
         <v>179</v>
       </c>
@@ -4660,32 +4663,32 @@
         <v>35</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D81" s="6">
         <v>1</v>
       </c>
       <c r="E81" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G81" s="7">
         <f t="shared" si="0"/>
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="H81" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>189</v>
+        <v>44</v>
       </c>
       <c r="J81" s="10" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="26" t="s">
         <v>179</v>
       </c>
@@ -4693,20 +4696,20 @@
         <v>35</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D82" s="6">
         <v>1</v>
       </c>
       <c r="E82" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G82" s="7">
-        <f t="shared" ref="G82" si="6">D82*E82</f>
-        <v>9900</v>
+        <f t="shared" si="0"/>
+        <v>10500</v>
       </c>
       <c r="H82" s="13" t="s">
         <v>182</v>
@@ -4718,7 +4721,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="26" t="s">
         <v>179</v>
       </c>
@@ -4726,20 +4729,20 @@
         <v>35</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>294</v>
+        <v>190</v>
       </c>
       <c r="D83" s="6">
         <v>1</v>
       </c>
       <c r="E83" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G83" s="7">
-        <f t="shared" si="0"/>
-        <v>9900</v>
+        <f t="shared" ref="G83" si="6">D83*E83</f>
+        <v>10500</v>
       </c>
       <c r="H83" s="13" t="s">
         <v>182</v>
@@ -4751,7 +4754,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="26" t="s">
         <v>179</v>
       </c>
@@ -4759,32 +4762,32 @@
         <v>35</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>191</v>
+        <v>292</v>
       </c>
       <c r="D84" s="6">
         <v>1</v>
       </c>
       <c r="E84" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G84" s="7">
         <f t="shared" si="0"/>
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="H84" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="26" t="s">
         <v>179</v>
       </c>
@@ -4792,32 +4795,32 @@
         <v>35</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D85" s="6">
         <v>1</v>
       </c>
       <c r="E85" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G85" s="7">
         <f t="shared" si="0"/>
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="H85" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>108</v>
+        <v>192</v>
       </c>
       <c r="J85" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="26" t="s">
         <v>179</v>
       </c>
@@ -4825,35 +4828,35 @@
         <v>35</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D86" s="6">
         <v>1</v>
       </c>
       <c r="E86" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G86" s="7">
         <f t="shared" si="0"/>
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="H86" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>195</v>
+        <v>108</v>
       </c>
       <c r="J86" s="10" t="s">
-        <v>195</v>
+        <v>108</v>
       </c>
       <c r="K86" s="41" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="26" t="s">
         <v>179</v>
       </c>
@@ -4861,35 +4864,35 @@
         <v>35</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D87" s="6">
         <v>1</v>
       </c>
       <c r="E87" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G87" s="7">
         <f t="shared" si="0"/>
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="H87" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K87" s="41" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="26" t="s">
         <v>179</v>
       </c>
@@ -4897,20 +4900,20 @@
         <v>35</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D88" s="6">
         <v>1</v>
       </c>
       <c r="E88" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G88" s="7">
         <f t="shared" si="0"/>
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="H88" s="13" t="s">
         <v>182</v>
@@ -4925,7 +4928,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="26" t="s">
         <v>179</v>
       </c>
@@ -4933,35 +4936,35 @@
         <v>35</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D89" s="6">
         <v>1</v>
       </c>
       <c r="E89" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G89" s="7">
         <f t="shared" si="0"/>
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="H89" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J89" s="10" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K89" s="41" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="26" t="s">
         <v>179</v>
       </c>
@@ -4969,35 +4972,35 @@
         <v>35</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D90" s="6">
         <v>1</v>
       </c>
       <c r="E90" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G90" s="7">
-        <f>D90*E90</f>
-        <v>9900</v>
+        <f t="shared" si="0"/>
+        <v>10500</v>
       </c>
       <c r="H90" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="J90" s="10" t="s">
-        <v>42</v>
+        <v>201</v>
       </c>
       <c r="K90" s="41" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="26" t="s">
         <v>179</v>
       </c>
@@ -5005,35 +5008,35 @@
         <v>35</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D91" s="6">
         <v>1</v>
       </c>
       <c r="E91" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G91" s="7">
         <f>D91*E91</f>
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="H91" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J91" s="10" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="K91" s="41" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="26" t="s">
         <v>179</v>
       </c>
@@ -5041,35 +5044,35 @@
         <v>35</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D92" s="6">
         <v>1</v>
       </c>
       <c r="E92" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G92" s="7">
         <f>D92*E92</f>
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="H92" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>205</v>
+        <v>62</v>
       </c>
       <c r="J92" s="10" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="K92" s="41" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="26" t="s">
         <v>179</v>
       </c>
@@ -5077,20 +5080,20 @@
         <v>35</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D93" s="6">
         <v>1</v>
       </c>
       <c r="E93" s="7">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G93" s="7">
-        <f t="shared" ref="G93" si="7">D93*E93</f>
-        <v>9900</v>
+        <f>D93*E93</f>
+        <v>10500</v>
       </c>
       <c r="H93" s="13" t="s">
         <v>182</v>
@@ -5099,13 +5102,13 @@
         <v>205</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>207</v>
+        <v>16</v>
       </c>
       <c r="K93" s="41" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="26" t="s">
         <v>179</v>
       </c>
@@ -5113,20 +5116,20 @@
         <v>35</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>266</v>
+        <v>206</v>
       </c>
       <c r="D94" s="6">
         <v>1</v>
       </c>
       <c r="E94" s="7">
-        <v>18900</v>
-      </c>
-      <c r="F94" s="28" t="s">
-        <v>210</v>
+        <v>10500</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="G94" s="7">
-        <f>D94*E94</f>
-        <v>18900</v>
+        <f t="shared" ref="G94" si="7">D94*E94</f>
+        <v>10500</v>
       </c>
       <c r="H94" s="13" t="s">
         <v>182</v>
@@ -5135,13 +5138,13 @@
         <v>205</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>267</v>
+        <v>207</v>
       </c>
       <c r="K94" s="41" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="26" t="s">
         <v>179</v>
       </c>
@@ -5149,35 +5152,35 @@
         <v>35</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>209</v>
+        <v>266</v>
       </c>
       <c r="D95" s="6">
         <v>1</v>
       </c>
       <c r="E95" s="7">
-        <v>21900</v>
+        <v>18900</v>
       </c>
       <c r="F95" s="28" t="s">
         <v>210</v>
       </c>
       <c r="G95" s="7">
         <f>D95*E95</f>
-        <v>21900</v>
+        <v>18900</v>
       </c>
       <c r="H95" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="J95" s="10" t="s">
-        <v>211</v>
+        <v>267</v>
       </c>
       <c r="K95" s="41" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="26" t="s">
         <v>179</v>
       </c>
@@ -5185,35 +5188,35 @@
         <v>35</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D96" s="6">
         <v>1</v>
       </c>
       <c r="E96" s="7">
-        <v>16900</v>
+        <v>23500</v>
       </c>
       <c r="F96" s="28" t="s">
         <v>210</v>
       </c>
       <c r="G96" s="7">
         <f>D96*E96</f>
-        <v>16900</v>
+        <v>23500</v>
       </c>
       <c r="H96" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>42</v>
+        <v>211</v>
       </c>
       <c r="J96" s="10" t="s">
-        <v>42</v>
+        <v>211</v>
       </c>
       <c r="K96" s="41" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="26" t="s">
         <v>179</v>
       </c>
@@ -5221,7 +5224,7 @@
         <v>35</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D97" s="6">
         <v>1</v>
@@ -5233,7 +5236,7 @@
         <v>210</v>
       </c>
       <c r="G97" s="7">
-        <f t="shared" ref="G97" si="8">D97*E97</f>
+        <f>D97*E97</f>
         <v>17900</v>
       </c>
       <c r="H97" s="13" t="s">
@@ -5246,7 +5249,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="26" t="s">
         <v>179</v>
       </c>
@@ -5254,35 +5257,32 @@
         <v>35</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>276</v>
+        <v>213</v>
       </c>
       <c r="D98" s="6">
         <v>1</v>
       </c>
       <c r="E98" s="7">
-        <v>16900</v>
+        <v>18900</v>
       </c>
       <c r="F98" s="28" t="s">
         <v>210</v>
       </c>
       <c r="G98" s="7">
-        <f>D98*E98</f>
-        <v>16900</v>
+        <f t="shared" ref="G98" si="8">D98*E98</f>
+        <v>18900</v>
       </c>
       <c r="H98" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>277</v>
+        <v>42</v>
       </c>
       <c r="J98" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="K98" s="41" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="26" t="s">
         <v>179</v>
       </c>
@@ -5290,32 +5290,32 @@
         <v>35</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>202</v>
+        <v>276</v>
       </c>
       <c r="D99" s="6">
         <v>1</v>
       </c>
       <c r="E99" s="7">
-        <v>8900</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>46</v>
+        <v>17900</v>
+      </c>
+      <c r="F99" s="28" t="s">
+        <v>210</v>
       </c>
       <c r="G99" s="7">
         <f>D99*E99</f>
-        <v>8900</v>
+        <v>17900</v>
       </c>
       <c r="H99" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>52</v>
+        <v>277</v>
       </c>
       <c r="J99" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="26" t="s">
         <v>179</v>
       </c>
@@ -5323,20 +5323,20 @@
         <v>35</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D100" s="6">
         <v>1</v>
       </c>
       <c r="E100" s="7">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G100" s="7">
-        <f t="shared" si="0"/>
-        <v>8900</v>
+        <f>D100*E100</f>
+        <v>9500</v>
       </c>
       <c r="H100" s="13" t="s">
         <v>182</v>
@@ -5348,7 +5348,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="26" t="s">
         <v>179</v>
       </c>
@@ -5356,20 +5356,20 @@
         <v>35</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D101" s="6">
         <v>1</v>
       </c>
       <c r="E101" s="7">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G101" s="7">
         <f t="shared" si="0"/>
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="H101" s="13" t="s">
         <v>182</v>
@@ -5381,76 +5381,76 @@
         <v>52</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D102" s="11">
+        <v>215</v>
+      </c>
+      <c r="D102" s="6">
         <v>1</v>
       </c>
       <c r="E102" s="7">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G102" s="7">
         <f t="shared" si="0"/>
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="H102" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="I102" s="16" t="s">
+      <c r="I102" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J102" s="16" t="s">
+      <c r="J102" s="10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B103" s="14" t="s">
+      <c r="B103" s="15" t="s">
         <v>35</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="D103" s="6">
+        <v>216</v>
+      </c>
+      <c r="D103" s="11">
         <v>1</v>
       </c>
       <c r="E103" s="7">
-        <v>10900</v>
+        <v>9500</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G103" s="7">
-        <f>D103*E103</f>
-        <v>10900</v>
+        <f t="shared" si="0"/>
+        <v>9500</v>
       </c>
       <c r="H103" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="I103" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="J103" s="10" t="s">
-        <v>47</v>
+      <c r="I103" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="J103" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="K103" s="41" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="26" t="s">
         <v>179</v>
       </c>
@@ -5458,20 +5458,20 @@
         <v>35</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="D104" s="6">
         <v>1</v>
       </c>
       <c r="E104" s="7">
-        <v>11900</v>
+        <v>12500</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G104" s="7">
         <f>D104*E104</f>
-        <v>11900</v>
+        <v>12500</v>
       </c>
       <c r="H104" s="13" t="s">
         <v>182</v>
@@ -5483,10 +5483,10 @@
         <v>47</v>
       </c>
       <c r="K104" s="41" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="26" t="s">
         <v>179</v>
       </c>
@@ -5494,35 +5494,35 @@
         <v>35</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>217</v>
+        <v>282</v>
       </c>
       <c r="D105" s="6">
         <v>1</v>
       </c>
       <c r="E105" s="7">
-        <v>10900</v>
+        <v>13500</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G105" s="7">
-        <f t="shared" si="0"/>
-        <v>10900</v>
+        <f>D105*E105</f>
+        <v>13500</v>
       </c>
       <c r="H105" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="J105" s="10" t="s">
-        <v>218</v>
+        <v>47</v>
       </c>
       <c r="K105" s="41" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="26" t="s">
         <v>179</v>
       </c>
@@ -5530,32 +5530,32 @@
         <v>35</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D106" s="6">
         <v>1</v>
       </c>
       <c r="E106" s="7">
-        <v>8900</v>
+        <v>12500</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G106" s="7">
         <f t="shared" si="0"/>
-        <v>8900</v>
+        <v>12500</v>
       </c>
       <c r="H106" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>220</v>
+        <v>52</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="26" t="s">
         <v>179</v>
       </c>
@@ -5563,35 +5563,35 @@
         <v>35</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D107" s="6">
         <v>1</v>
       </c>
       <c r="E107" s="7">
-        <v>9500</v>
+        <v>8900</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G107" s="7">
         <f t="shared" si="0"/>
-        <v>9500</v>
+        <v>8900</v>
       </c>
       <c r="H107" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="J107" s="10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K107" s="41" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="26" t="s">
         <v>179</v>
       </c>
@@ -5599,32 +5599,32 @@
         <v>35</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D108" s="6">
         <v>1</v>
       </c>
       <c r="E108" s="7">
-        <v>10900</v>
-      </c>
-      <c r="F108" s="29" t="s">
+        <v>9500</v>
+      </c>
+      <c r="F108" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G108" s="7">
         <f t="shared" si="0"/>
-        <v>10900</v>
+        <v>9500</v>
       </c>
       <c r="H108" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>98</v>
+        <v>223</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="26" t="s">
         <v>179</v>
       </c>
@@ -5632,35 +5632,35 @@
         <v>35</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D109" s="6">
         <v>1</v>
       </c>
       <c r="E109" s="7">
-        <v>13500</v>
-      </c>
-      <c r="F109" s="30" t="s">
-        <v>226</v>
+        <v>12500</v>
+      </c>
+      <c r="F109" s="29" t="s">
+        <v>46</v>
       </c>
       <c r="G109" s="7">
         <f t="shared" si="0"/>
-        <v>13500</v>
+        <v>12500</v>
       </c>
       <c r="H109" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>170</v>
+        <v>98</v>
       </c>
       <c r="J109" s="10" t="s">
-        <v>170</v>
+        <v>99</v>
       </c>
       <c r="K109" s="41" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="26" t="s">
         <v>179</v>
       </c>
@@ -5668,71 +5668,71 @@
         <v>35</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D110" s="6">
         <v>1</v>
       </c>
       <c r="E110" s="7">
-        <v>13500</v>
+        <v>15900</v>
       </c>
       <c r="F110" s="30" t="s">
         <v>226</v>
       </c>
       <c r="G110" s="7">
         <f t="shared" si="0"/>
-        <v>13500</v>
+        <v>15900</v>
       </c>
       <c r="H110" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I110" s="10" t="s">
-        <v>228</v>
+        <v>170</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>228</v>
+        <v>170</v>
       </c>
       <c r="K110" s="41" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B111" s="15" t="s">
+      <c r="B111" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D111" s="11">
+        <v>227</v>
+      </c>
+      <c r="D111" s="6">
         <v>1</v>
       </c>
       <c r="E111" s="7">
-        <v>23900</v>
-      </c>
-      <c r="F111" s="31" t="s">
-        <v>33</v>
+        <v>15900</v>
+      </c>
+      <c r="F111" s="30" t="s">
+        <v>226</v>
       </c>
       <c r="G111" s="7">
-        <f>D111*E111</f>
-        <v>23900</v>
+        <f t="shared" si="0"/>
+        <v>15900</v>
       </c>
       <c r="H111" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="I111" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="J111" s="16" t="s">
-        <v>42</v>
+      <c r="I111" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="J111" s="10" t="s">
+        <v>228</v>
       </c>
       <c r="K111" s="41" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="26" t="s">
         <v>179</v>
       </c>
@@ -5740,20 +5740,20 @@
         <v>35</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D112" s="11">
         <v>1</v>
       </c>
       <c r="E112" s="7">
-        <v>23900</v>
+        <v>25500</v>
       </c>
       <c r="F112" s="31" t="s">
         <v>33</v>
       </c>
       <c r="G112" s="7">
-        <f t="shared" si="0"/>
-        <v>23900</v>
+        <f>D112*E112</f>
+        <v>25500</v>
       </c>
       <c r="H112" s="13" t="s">
         <v>182</v>
@@ -5768,7 +5768,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="26" t="s">
         <v>179</v>
       </c>
@@ -5776,20 +5776,20 @@
         <v>35</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D113" s="11">
         <v>1</v>
       </c>
       <c r="E113" s="7">
-        <v>16900</v>
+        <v>25500</v>
       </c>
       <c r="F113" s="31" t="s">
         <v>33</v>
       </c>
       <c r="G113" s="7">
-        <f>D113*E113</f>
-        <v>16900</v>
+        <f t="shared" si="0"/>
+        <v>25500</v>
       </c>
       <c r="H113" s="13" t="s">
         <v>182</v>
@@ -5804,40 +5804,40 @@
         <v>231</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B114" s="14" t="s">
+      <c r="B114" s="15" t="s">
         <v>35</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D114" s="6">
+        <v>231</v>
+      </c>
+      <c r="D114" s="11">
         <v>1</v>
       </c>
       <c r="E114" s="7">
-        <v>16900</v>
-      </c>
-      <c r="F114" s="12" t="s">
+        <v>19900</v>
+      </c>
+      <c r="F114" s="31" t="s">
         <v>33</v>
       </c>
       <c r="G114" s="7">
-        <f t="shared" si="0"/>
-        <v>16900</v>
+        <f>D114*E114</f>
+        <v>19900</v>
       </c>
       <c r="H114" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="I114" s="10" t="s">
+      <c r="I114" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="J114" s="10" t="s">
+      <c r="J114" s="16" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="26" t="s">
         <v>179</v>
       </c>
@@ -5845,20 +5845,20 @@
         <v>35</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D115" s="6">
         <v>1</v>
       </c>
       <c r="E115" s="7">
-        <v>16900</v>
-      </c>
-      <c r="F115" s="17" t="s">
-        <v>65</v>
+        <v>19900</v>
+      </c>
+      <c r="F115" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="G115" s="7">
         <f t="shared" si="0"/>
-        <v>16900</v>
+        <v>19900</v>
       </c>
       <c r="H115" s="13" t="s">
         <v>182</v>
@@ -5870,112 +5870,112 @@
         <v>42</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B116" s="32" t="s">
-        <v>234</v>
+      <c r="B116" s="14" t="s">
+        <v>35</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D116" s="6">
         <v>1</v>
       </c>
       <c r="E116" s="7">
-        <v>27000</v>
-      </c>
-      <c r="F116" s="8" t="s">
-        <v>13</v>
+        <v>19900</v>
+      </c>
+      <c r="F116" s="17" t="s">
+        <v>65</v>
       </c>
       <c r="G116" s="7">
         <f t="shared" si="0"/>
-        <v>27000</v>
+        <v>19900</v>
       </c>
       <c r="H116" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I116" s="10" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B117" s="23" t="s">
-        <v>140</v>
+      <c r="B117" s="32" t="s">
+        <v>234</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D117" s="6">
         <v>1</v>
       </c>
       <c r="E117" s="7">
-        <v>11900</v>
-      </c>
-      <c r="F117" s="12" t="s">
-        <v>33</v>
+        <v>27000</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="G117" s="7">
-        <f t="shared" ref="G117" si="9">D117*E117</f>
-        <v>11900</v>
+        <f t="shared" si="0"/>
+        <v>27000</v>
       </c>
       <c r="H117" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I117" s="10" t="s">
-        <v>237</v>
+        <v>56</v>
       </c>
       <c r="J117" s="10" t="s">
-        <v>238</v>
+        <v>56</v>
       </c>
       <c r="K117" s="41" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B118" s="18" t="s">
-        <v>73</v>
+      <c r="B118" s="23" t="s">
+        <v>140</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>296</v>
+        <v>236</v>
       </c>
       <c r="D118" s="6">
         <v>1</v>
       </c>
       <c r="E118" s="7">
-        <v>17900</v>
+        <v>11900</v>
       </c>
       <c r="F118" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G118" s="7">
-        <f t="shared" si="0"/>
-        <v>17900</v>
+        <f t="shared" ref="G118" si="9">D118*E118</f>
+        <v>11900</v>
       </c>
       <c r="H118" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="J118" s="10" t="s">
-        <v>75</v>
+        <v>238</v>
       </c>
       <c r="K118" s="41" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="26" t="s">
         <v>179</v>
       </c>
@@ -5983,20 +5983,20 @@
         <v>73</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="D119" s="6">
         <v>1</v>
       </c>
       <c r="E119" s="7">
-        <v>18900</v>
+        <v>25100</v>
       </c>
       <c r="F119" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G119" s="7">
-        <f t="shared" ref="G119" si="10">D119*E119</f>
-        <v>18900</v>
+        <f t="shared" si="0"/>
+        <v>25100</v>
       </c>
       <c r="H119" s="13" t="s">
         <v>182</v>
@@ -6008,98 +6008,98 @@
         <v>75</v>
       </c>
       <c r="K119" s="41" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B120" s="3" t="s">
-        <v>70</v>
+      <c r="B120" s="18" t="s">
+        <v>73</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>239</v>
+        <v>311</v>
       </c>
       <c r="D120" s="6">
         <v>1</v>
       </c>
       <c r="E120" s="7">
-        <v>13000</v>
-      </c>
-      <c r="F120" s="8" t="s">
-        <v>13</v>
+        <v>19800</v>
+      </c>
+      <c r="F120" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="G120" s="7">
-        <f t="shared" si="0"/>
-        <v>13000</v>
+        <f t="shared" ref="G120" si="10">D120*E120</f>
+        <v>19800</v>
       </c>
       <c r="H120" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I120" s="10" t="s">
-        <v>240</v>
+        <v>75</v>
       </c>
       <c r="J120" s="10" t="s">
-        <v>240</v>
+        <v>75</v>
       </c>
       <c r="K120" s="41" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B121" s="33" t="s">
+      <c r="B121" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D121" s="11">
+        <v>239</v>
+      </c>
+      <c r="D121" s="6">
         <v>1</v>
       </c>
       <c r="E121" s="7">
-        <v>12000</v>
-      </c>
-      <c r="F121" s="27" t="s">
+        <v>13000</v>
+      </c>
+      <c r="F121" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G121" s="7">
         <f t="shared" si="0"/>
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="H121" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="I121" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="J121" s="16" t="s">
-        <v>242</v>
+      <c r="I121" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="J121" s="10" t="s">
+        <v>240</v>
       </c>
       <c r="K121" s="41" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="B122" s="33" t="s">
         <v>70</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D122" s="6">
+        <v>241</v>
+      </c>
+      <c r="D122" s="11">
         <v>1</v>
       </c>
       <c r="E122" s="7">
         <v>12000</v>
       </c>
-      <c r="F122" s="8" t="s">
+      <c r="F122" s="27" t="s">
         <v>13</v>
       </c>
       <c r="G122" s="7">
@@ -6109,17 +6109,17 @@
       <c r="H122" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="I122" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J122" s="10" t="s">
-        <v>16</v>
+      <c r="I122" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J122" s="16" t="s">
+        <v>242</v>
       </c>
       <c r="K122" s="41" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="26" t="s">
         <v>179</v>
       </c>
@@ -6127,71 +6127,71 @@
         <v>70</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D123" s="6">
         <v>1</v>
       </c>
       <c r="E123" s="7">
-        <v>15000</v>
-      </c>
-      <c r="F123" s="28" t="s">
-        <v>210</v>
+        <v>12000</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="G123" s="7">
         <f t="shared" si="0"/>
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="H123" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I123" s="10" t="s">
-        <v>245</v>
+        <v>16</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>246</v>
+        <v>16</v>
       </c>
       <c r="K123" s="41" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B124" s="22" t="s">
-        <v>136</v>
+      <c r="B124" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D124" s="6">
         <v>1</v>
       </c>
       <c r="E124" s="7">
-        <v>10000</v>
-      </c>
-      <c r="F124" s="8" t="s">
-        <v>13</v>
+        <v>15000</v>
+      </c>
+      <c r="F124" s="28" t="s">
+        <v>210</v>
       </c>
       <c r="G124" s="7">
         <f t="shared" si="0"/>
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="H124" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I124" s="10" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J124" s="10" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="K124" s="41" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="26" t="s">
         <v>179</v>
       </c>
@@ -6199,35 +6199,35 @@
         <v>136</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D125" s="6">
         <v>1</v>
       </c>
       <c r="E125" s="7">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G125" s="7">
-        <f t="shared" ref="G125" si="11">D125*E125</f>
-        <v>10000</v>
+        <f t="shared" si="0"/>
+        <v>12000</v>
       </c>
       <c r="H125" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I125" s="10" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K125" s="41" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="26" t="s">
         <v>179</v>
       </c>
@@ -6235,20 +6235,20 @@
         <v>136</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>285</v>
+        <v>249</v>
       </c>
       <c r="D126" s="6">
         <v>1</v>
       </c>
       <c r="E126" s="7">
-        <v>8500</v>
+        <v>12000</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G126" s="7">
-        <f>D126*E126</f>
-        <v>8500</v>
+        <f t="shared" ref="G126" si="11">D126*E126</f>
+        <v>12000</v>
       </c>
       <c r="H126" s="13" t="s">
         <v>182</v>
@@ -6260,10 +6260,10 @@
         <v>250</v>
       </c>
       <c r="K126" s="41" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="26" t="s">
         <v>179</v>
       </c>
@@ -6271,7 +6271,7 @@
         <v>136</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="D127" s="6">
         <v>1</v>
@@ -6290,16 +6290,16 @@
         <v>182</v>
       </c>
       <c r="I127" s="10" t="s">
-        <v>308</v>
+        <v>250</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>308</v>
+        <v>250</v>
       </c>
       <c r="K127" s="41" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="26" t="s">
         <v>179</v>
       </c>
@@ -6307,7 +6307,7 @@
         <v>136</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>251</v>
+        <v>305</v>
       </c>
       <c r="D128" s="6">
         <v>1</v>
@@ -6319,20 +6319,20 @@
         <v>13</v>
       </c>
       <c r="G128" s="7">
-        <f t="shared" si="0"/>
+        <f>D128*E128</f>
         <v>12000</v>
       </c>
       <c r="H128" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I128" s="10" t="s">
-        <v>252</v>
+        <v>306</v>
       </c>
       <c r="J128" s="10" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="26" t="s">
         <v>179</v>
       </c>
@@ -6340,35 +6340,35 @@
         <v>136</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D129" s="6">
         <v>1</v>
       </c>
       <c r="E129" s="7">
-        <v>16000</v>
-      </c>
-      <c r="F129" s="28" t="s">
-        <v>210</v>
+        <v>12000</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="G129" s="7">
         <f t="shared" si="0"/>
-        <v>16000</v>
+        <v>12000</v>
       </c>
       <c r="H129" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I129" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K129" s="41" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="26" t="s">
         <v>179</v>
       </c>
@@ -6376,35 +6376,35 @@
         <v>136</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D130" s="6">
         <v>1</v>
       </c>
       <c r="E130" s="7">
-        <v>8000</v>
-      </c>
-      <c r="F130" s="12" t="s">
-        <v>33</v>
+        <v>18000</v>
+      </c>
+      <c r="F130" s="28" t="s">
+        <v>210</v>
       </c>
       <c r="G130" s="7">
         <f t="shared" si="0"/>
-        <v>8000</v>
+        <v>18000</v>
       </c>
       <c r="H130" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I130" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J130" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K130" s="50" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="26" t="s">
         <v>179</v>
       </c>
@@ -6412,20 +6412,20 @@
         <v>136</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>295</v>
+        <v>255</v>
       </c>
       <c r="D131" s="6">
         <v>1</v>
       </c>
       <c r="E131" s="7">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="F131" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G131" s="7">
-        <f t="shared" ref="G131:G132" si="12">D131*E131</f>
-        <v>11000</v>
+        <f t="shared" si="0"/>
+        <v>10000</v>
       </c>
       <c r="H131" s="13" t="s">
         <v>182</v>
@@ -6437,1173 +6437,1205 @@
         <v>256</v>
       </c>
       <c r="K131" s="50" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B132" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C132" s="48" t="s">
-        <v>288</v>
+      <c r="B132" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="D132" s="6">
         <v>1</v>
       </c>
       <c r="E132" s="7">
-        <v>52000</v>
+        <v>11000</v>
       </c>
       <c r="F132" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G132" s="7">
+        <f t="shared" ref="G132:G133" si="12">D132*E132</f>
+        <v>11000</v>
+      </c>
+      <c r="H132" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="I132" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="J132" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="K132" s="50" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A133" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B133" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C133" s="48" t="s">
+        <v>287</v>
+      </c>
+      <c r="D133" s="6">
+        <v>1</v>
+      </c>
+      <c r="E133" s="7">
+        <v>52000</v>
+      </c>
+      <c r="F133" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G133" s="7">
         <f t="shared" si="12"/>
         <v>52000</v>
       </c>
-      <c r="H132" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="I132" s="49" t="s">
+      <c r="H133" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="I133" s="49" t="s">
+        <v>288</v>
+      </c>
+      <c r="J133" s="49" t="s">
         <v>289</v>
-      </c>
-      <c r="J132" s="49" t="s">
-        <v>290</v>
-      </c>
-      <c r="K132" s="50" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="B133" s="43" t="s">
-        <v>268</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="D133" s="6">
-        <v>1</v>
-      </c>
-      <c r="E133" s="7">
-        <v>16000</v>
-      </c>
-      <c r="F133" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G133" s="7">
-        <f t="shared" si="0"/>
-        <v>16000</v>
-      </c>
-      <c r="H133" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="I133" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="J133" s="10" t="s">
-        <v>270</v>
       </c>
       <c r="K133" s="41" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A134" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B134" s="34" t="s">
-        <v>257</v>
+      <c r="B134" s="43" t="s">
+        <v>268</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="D134" s="6">
         <v>1</v>
       </c>
       <c r="E134" s="7">
-        <v>17000</v>
-      </c>
-      <c r="F134" s="28" t="s">
-        <v>210</v>
+        <v>16000</v>
+      </c>
+      <c r="F134" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="G134" s="7">
-        <f t="shared" ref="G134" si="13">D134*E134</f>
-        <v>17000</v>
+        <f t="shared" si="0"/>
+        <v>16000</v>
       </c>
       <c r="H134" s="13" t="s">
         <v>182</v>
       </c>
       <c r="I134" s="10" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="J134" s="10" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="K134" s="41" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="3" t="s">
+    <row r="135" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A135" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B135" s="34" t="s">
+        <v>257</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D135" s="6">
+        <v>1</v>
+      </c>
+      <c r="E135" s="7">
+        <v>17000</v>
+      </c>
+      <c r="F135" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G135" s="7">
+        <f t="shared" ref="G135" si="13">D135*E135</f>
+        <v>17000</v>
+      </c>
+      <c r="H135" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="I135" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="J135" s="10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A136" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B136" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C135" s="3" t="s">
+      <c r="C136" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D135" s="3" t="s">
+      <c r="D136" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E135" s="3" t="s">
+      <c r="E136" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="F135" s="3" t="s">
+      <c r="F136" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G135" s="3" t="s">
+      <c r="G136" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H135" s="3" t="s">
+      <c r="H136" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="I135" s="3" t="s">
+      <c r="I136" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="J135" s="3" t="s">
+      <c r="J136" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="4" t="str">
-        <f>"En curso = " &amp; COUNTA(A2:A30)</f>
-        <v>En curso = 29</v>
-      </c>
-      <c r="B136" s="14" t="str">
-        <f>"Ivrea = " &amp; COUNTA(B14:B27,B36:B53,B67:B115)</f>
-        <v>Ivrea = 81</v>
-      </c>
-      <c r="C136" s="45" t="str">
-        <f>"Series en total = " &amp; COUNTA(C2:C134)</f>
-        <v>Series en total = 133</v>
-      </c>
-      <c r="D136" s="6">
-        <f>SUM(D2:D134)</f>
-        <v>609</v>
-      </c>
-      <c r="E136" s="7">
-        <f>SUM(E2:E134)</f>
-        <v>1665500</v>
-      </c>
-      <c r="F136" s="46" t="str">
-        <f>"B6 = " &amp; COUNTA(F2:F12,F14:F43,F28,F31:F35,F40:F54,F60:F62,F64:F66,F74:F93,F116,F120:F122,F124:F128)</f>
-        <v>B6 = 97</v>
-      </c>
-      <c r="G136" s="7">
-        <f>SUM(G2:G134)</f>
-        <v>6794800</v>
-      </c>
-      <c r="H136" s="13" t="str">
-        <f>"Finalizados = " &amp; COUNTA(H29:H29,H31:H63,H65:H68,H74,H76:H134)</f>
-        <v>Finalizados = 98</v>
-      </c>
-      <c r="I136" s="46" t="str">
-        <f>"B6 = " &amp; SUM(D2:D12,D14:D43,D28,D31:D35,D40:D54,D60:D62,D64:D66,D74:D93,D116,D120:D122,D124:D128)</f>
-        <v>B6 = 644</v>
-      </c>
-      <c r="J136" s="35" t="str">
-        <f>"Series = " &amp; COUNTA(K2:K19,K21:K26,K28:K31,K34:K35,K38:K45,K54:K61,K63,K76,K86:K96,K98,K104:K105,K107,K109:K113,K117:K127,K129:K134)</f>
+    <row r="137" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A137" s="4" t="str">
+        <f>"En curso = " &amp; COUNTA(A2:A29)</f>
+        <v>En curso = 28</v>
+      </c>
+      <c r="B137" s="14" t="str">
+        <f>"Ivrea = " &amp; COUNTA(B14:B26,B35:B54,B68:B116)</f>
+        <v>Ivrea = 82</v>
+      </c>
+      <c r="C137" s="45" t="str">
+        <f>"Series en total = " &amp; COUNTA(C2:C135)</f>
+        <v>Series en total = 134</v>
+      </c>
+      <c r="D137" s="6">
+        <f>SUM(D2:D135)</f>
+        <v>630</v>
+      </c>
+      <c r="E137" s="7">
+        <f>SUM(E2:E135)</f>
+        <v>1773200</v>
+      </c>
+      <c r="F137" s="46" t="str">
+        <f>"B6 = " &amp; COUNTA(F2:F12,F14:F34,F27,F30:F34,F40:F55,F61:F63,F65:F67,F75:F94,F117,F121:F123,F125:F129)</f>
+        <v>B6 = 89</v>
+      </c>
+      <c r="G137" s="7">
+        <f>SUM(G2:G135)</f>
+        <v>7364800</v>
+      </c>
+      <c r="H137" s="13" t="str">
+        <f>"Finalizados = " &amp; COUNTA(H28:H28,H30:H64,H66:H69,H75,H77:H135)</f>
+        <v>Finalizados = 100</v>
+      </c>
+      <c r="I137" s="46" t="str">
+        <f>"B6 = " &amp; SUM(D2:D12,D14:D15,D27,D30:D34,D40:D55,D61:D63,D65:D67,D75:D94,D117,D121:D123,D125:D129)</f>
+        <v>B6 = 329</v>
+      </c>
+      <c r="J137" s="35" t="str">
+        <f>"Series = " &amp; COUNTA(K2:K18,K20:K25,K27:K30,K33:K34,K37:K45,K54:K61,K63,K76,K86:K96,K103:K105,K107,K109:K113,K117:K127,K129:K134)</f>
         <v>Series = 85</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="20" t="str">
-        <f>"Completado = " &amp; COUNTA(A31:A63)</f>
-        <v>Completado = 33</v>
-      </c>
-      <c r="B137" s="5" t="str">
-        <f>"Panini = " &amp; COUNTA(B2:B13,B31:B35,B64:B66)</f>
+    <row r="138" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A138" s="20" t="str">
+        <f>"Completado = " &amp; COUNTA(A30:A64)</f>
+        <v>Completado = 35</v>
+      </c>
+      <c r="B138" s="5" t="str">
+        <f>"Panini = " &amp; COUNTA(B2:B13,B30:B34,B65:B67)</f>
         <v>Panini = 20</v>
       </c>
-      <c r="F137" s="39" t="str">
-        <f>"C6 = " &amp; COUNTA(F17:F25,F36:F39,F63,F67:F73,F99:F108)</f>
+      <c r="F138" s="39" t="str">
+        <f>"C6 = " &amp; COUNTA(F16:F24,F35:F38,F64,F68:F74,F100:F109)</f>
         <v>C6 = 31</v>
       </c>
-      <c r="H137" s="9" t="str">
-        <f>"En publicación = " &amp; COUNTA(H2:H28,H30,H64,H69:H73,H75)</f>
-        <v>En publicación = 35</v>
-      </c>
-      <c r="I137" s="39" t="str">
-        <f>"C6 = " &amp; SUM(D17:D25,D36:D39,D63,D67:D73,D99:D108)</f>
-        <v>C6 = 221</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="25" t="str">
-        <f>"Droppeado = " &amp; COUNTA(A64:A75)</f>
+      <c r="H138" s="9" t="str">
+        <f>"En publicación = " &amp; COUNTA(H2:H27,H29,H65,H70:H74,H76)</f>
+        <v>En publicación = 34</v>
+      </c>
+      <c r="I138" s="39" t="str">
+        <f>"C6 = " &amp; SUM(D16:D24,D35:D38,D64,D68:D74,D100:D109)</f>
+        <v>C6 = 230</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A139" s="25" t="str">
+        <f>"Droppeado = " &amp; COUNTA(A65:A76)</f>
         <v>Droppeado = 12</v>
       </c>
-      <c r="B138" s="22" t="str">
-        <f>"Kemuri = " &amp; COUNTA(B59,B124:B131)</f>
+      <c r="B139" s="22" t="str">
+        <f>"Kemuri = " &amp; COUNTA(B60,B125:B132)</f>
         <v>Kemuri = 9</v>
       </c>
-      <c r="F138" s="40" t="str">
-        <f>"A5 = H57" &amp; COUNTA(F13,F27,F29,F55:F59,F111:F114,F117:F118,F130:F133)</f>
+      <c r="F139" s="40" t="str">
+        <f>"A5 = H57" &amp; COUNTA(F13,F26,F28,F56:F60,F112:F115,F118:F119,F131:F134)</f>
         <v>A5 = H5718</v>
       </c>
-      <c r="I138" s="40" t="str">
-        <f>"A5 = " &amp; SUM(D13,D27,D29:D58,D56:D59,D111:D114,D117:D118,D130:D133)</f>
-        <v>A5 = 264</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="26" t="str">
-        <f>"Tomo único = " &amp; COUNTA(A76:A134)</f>
+      <c r="I139" s="40" t="str">
+        <f>"A5 = " &amp; SUM(D13,D26,D28,D56:D60,D112:D115,D118:D120,D131:D134)</f>
+        <v>A5 = 43</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A140" s="26" t="str">
+        <f>"Tomo único = " &amp; COUNTA(A77:A135)</f>
         <v>Tomo único = 59</v>
       </c>
-      <c r="B139" s="23" t="str">
-        <f>"Distrito Manga = " &amp; COUNTA(B60:B61,B118)</f>
+      <c r="B140" s="23" t="str">
+        <f>"Distrito Manga = " &amp; COUNTA(B61:B62,B119)</f>
         <v>Distrito Manga = 3</v>
       </c>
-      <c r="F139" s="28" t="str">
-        <f>"B6x2 = " &amp; COUNTA(F16,F94:F98,F123,F129,F134:F134)</f>
+      <c r="F140" s="28" t="str">
+        <f>"B6x2 = " &amp; COUNTA(F39,F95:F99,F124,F130,F135:F135)</f>
         <v>B6x2 = 9</v>
       </c>
-      <c r="I139" s="28" t="str">
-        <f>"B6x2 = " &amp; SUM(D94:D98,D123,D129,D134:D134)</f>
+      <c r="I140" s="28" t="str">
+        <f>"B6x2 = " &amp; SUM(D95:D99,D124,D130,D135:D135)</f>
         <v>B6x2 = 8</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B140" s="3" t="str">
-        <f>"Ovni Press = " &amp; COUNTA(B28,B120:B123)</f>
+    <row r="141" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B141" s="3" t="str">
+        <f>"Ovni Press = " &amp; COUNTA(B27,B121:B124)</f>
         <v>Ovni Press = 5</v>
       </c>
-      <c r="F140" s="30" t="str">
-        <f>"C6x2 = " &amp; COUNTA(F109:F110)</f>
+      <c r="F141" s="30" t="str">
+        <f>"C6x2 = " &amp; COUNTA(F110:F111)</f>
         <v>C6x2 = 2</v>
       </c>
-      <c r="I140" s="30" t="str">
-        <f>"C6x2 = " &amp; SUM(D109:D110)</f>
+      <c r="I141" s="30" t="str">
+        <f>"C6x2 = " &amp; SUM(D110:D111)</f>
         <v>C6x2 = 2</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B141" s="36" t="str">
-        <f>"Planeta Cómic = " &amp; COUNTA(B29:B29,B54:B56,B118)</f>
+    <row r="142" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B142" s="36" t="str">
+        <f>"Planeta Cómic = " &amp; COUNTA(B28:B28,B55:B57,B119)</f>
         <v>Planeta Cómic = 5</v>
       </c>
-      <c r="F141" s="17" t="str">
-        <f>"A5 color = " &amp; COUNTA(F26,F30,F115)</f>
+      <c r="F142" s="17" t="str">
+        <f>"A5 color = " &amp; COUNTA(F25,F29,F116)</f>
         <v>A5 color = 3</v>
       </c>
-      <c r="I141" s="17" t="str">
-        <f>"A5 color = " &amp; SUM(D115,D26,D30)</f>
-        <v>A5 color = 14</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B142" s="24" t="str">
-        <f>"Utopia = " &amp; COUNTA(B62:B63)</f>
+      <c r="I142" s="17" t="str">
+        <f>"A5 color = " &amp; SUM(D116,D25,D29)</f>
+        <v>A5 color = 15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B143" s="24" t="str">
+        <f>"Utopia = " &amp; COUNTA(B63:B64)</f>
         <v>Utopia = 2</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B143" s="21" t="str">
-        <f>"Merci = " &amp; COUNTA(B57)</f>
+    <row r="144" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B144" s="21" t="str">
+        <f>"Merci = " &amp; COUNTA(B58)</f>
         <v>Merci = 1</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B144" s="32" t="str">
-        <f>"Milky Way = " &amp; COUNTA(B116)</f>
+    <row r="145" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B145" s="32" t="str">
+        <f>"Milky Way = " &amp; COUNTA(B117)</f>
         <v>Milky Way = 1</v>
       </c>
     </row>
-    <row r="145" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B145" s="37" t="str">
-        <f>"Moztros = " &amp; COUNTA(B58,B134)</f>
+    <row r="146" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B146" s="37" t="str">
+        <f>"Moztros = " &amp; COUNTA(B59,B135)</f>
         <v>Moztros = 2</v>
       </c>
     </row>
-    <row r="146" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B146" s="38" t="str">
-        <f>"Random Comics = " &amp; COUNTA(B30)</f>
+    <row r="147" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B147" s="38" t="str">
+        <f>"Random Comics = " &amp; COUNTA(B29)</f>
         <v>Random Comics = 1</v>
       </c>
     </row>
-    <row r="147" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B147" s="43" t="str">
-        <f>"Hotel de las Ideas = " &amp; COUNTA(B133)</f>
+    <row r="148" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B148" s="43" t="str">
+        <f>"Hotel de las Ideas = " &amp; COUNTA(B134)</f>
         <v>Hotel de las Ideas = 1</v>
       </c>
     </row>
-    <row r="148" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B148" s="47" t="str">
-        <f>"Kibook Ediciones = " &amp; COUNTA(B132)</f>
+    <row r="149" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B149" s="47" t="str">
+        <f>"Kibook Ediciones = " &amp; COUNTA(B133)</f>
         <v>Kibook Ediciones = 1</v>
       </c>
     </row>
-    <row r="149" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="151" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="152" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="153" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="154" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="155" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="156" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="157" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="158" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="159" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="160" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <conditionalFormatting sqref="F2:F135">
+  <conditionalFormatting sqref="F2:F136">
     <cfRule type="cellIs" dxfId="12" priority="5" operator="equal">
       <formula>"B6"</formula>
     </cfRule>
@@ -7611,7 +7643,7 @@
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3 F36:F135 F7:F34">
+  <conditionalFormatting sqref="F3 F7:F33 F35:F136">
     <cfRule type="cellIs" dxfId="10" priority="45" operator="equal">
       <formula>"C6"</formula>
     </cfRule>
@@ -7619,7 +7651,7 @@
       <formula>"A5"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15:F16 F43">
+  <conditionalFormatting sqref="F43 F15 F39">
     <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"B6"</formula>
     </cfRule>
@@ -7647,7 +7679,7 @@
       <formula>"A5"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H6 H29 H65:H68 H74 H76:H135 H31:H63">
+  <conditionalFormatting sqref="H4:H6 H28 H66:H69 H75 H77:H136 H30:H64">
     <cfRule type="containsText" dxfId="0" priority="47" operator="containsText" text="En publicacion">
       <formula>NOT(ISERROR(SEARCH(("En publicacion"),(H4))))</formula>
     </cfRule>

--- a/assets/Mangas.xlsx
+++ b/assets/Mangas.xlsx
@@ -1,32 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nahue\Desktop\proyectos\mangas\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operador\Desktop\mangas-astro\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414E13CF-7005-4D23-9521-1F671A165925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63B1FB3-1CAB-43C0-80DC-59EAD1BF660D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1854,22 +1843,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.86328125" customWidth="1"/>
-    <col min="4" max="4" width="6.86328125" customWidth="1"/>
-    <col min="5" max="5" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.85546875" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.73046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.73046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.73046875" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.7109375" customWidth="1"/>
     <col min="11" max="11" width="52" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>271</v>
       </c>
@@ -1904,7 +1893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
@@ -1940,7 +1929,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -1976,7 +1965,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
@@ -2012,7 +2001,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
@@ -2048,7 +2037,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
@@ -2084,7 +2073,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
@@ -2120,7 +2109,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
@@ -2156,7 +2145,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -2192,7 +2181,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>10</v>
       </c>
@@ -2228,7 +2217,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
@@ -2264,7 +2253,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -2300,7 +2289,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>10</v>
       </c>
@@ -2336,7 +2325,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
@@ -2350,14 +2339,14 @@
         <v>9</v>
       </c>
       <c r="E14" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G14" s="7">
         <f t="shared" si="0"/>
-        <v>94500</v>
+        <v>108000</v>
       </c>
       <c r="H14" s="44" t="s">
         <v>273</v>
@@ -2372,7 +2361,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>10</v>
       </c>
@@ -2386,14 +2375,14 @@
         <v>5</v>
       </c>
       <c r="E15" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G15" s="7">
         <f t="shared" ref="G15" si="1">D15*E15</f>
-        <v>52500</v>
+        <v>60000</v>
       </c>
       <c r="H15" s="44" t="s">
         <v>273</v>
@@ -2408,7 +2397,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>10</v>
       </c>
@@ -2422,14 +2411,14 @@
         <v>15</v>
       </c>
       <c r="E16" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G16" s="7">
         <f t="shared" si="0"/>
-        <v>142500</v>
+        <v>165000</v>
       </c>
       <c r="H16" s="44" t="s">
         <v>273</v>
@@ -2444,7 +2433,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>10</v>
       </c>
@@ -2458,14 +2447,14 @@
         <v>35</v>
       </c>
       <c r="E17" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G17" s="7">
         <f t="shared" ref="G17" si="2">D17*E17</f>
-        <v>332500</v>
+        <v>385000</v>
       </c>
       <c r="H17" s="44" t="s">
         <v>273</v>
@@ -2480,7 +2469,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>10</v>
       </c>
@@ -2494,14 +2483,14 @@
         <v>8</v>
       </c>
       <c r="E18" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G18" s="7">
         <f t="shared" si="0"/>
-        <v>76000</v>
+        <v>88000</v>
       </c>
       <c r="H18" s="44" t="s">
         <v>273</v>
@@ -2516,7 +2505,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>10</v>
       </c>
@@ -2530,14 +2519,14 @@
         <v>21</v>
       </c>
       <c r="E19" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G19" s="7">
         <f t="shared" si="0"/>
-        <v>199500</v>
+        <v>231000</v>
       </c>
       <c r="H19" s="44" t="s">
         <v>273</v>
@@ -2549,7 +2538,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>10</v>
       </c>
@@ -2563,14 +2552,14 @@
         <v>18</v>
       </c>
       <c r="E20" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G20" s="7">
         <f t="shared" si="0"/>
-        <v>171000</v>
+        <v>198000</v>
       </c>
       <c r="H20" s="44" t="s">
         <v>273</v>
@@ -2585,7 +2574,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>10</v>
       </c>
@@ -2599,14 +2588,14 @@
         <v>20</v>
       </c>
       <c r="E21" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G21" s="7">
         <f t="shared" si="0"/>
-        <v>190000</v>
+        <v>220000</v>
       </c>
       <c r="H21" s="44" t="s">
         <v>273</v>
@@ -2621,7 +2610,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>10</v>
       </c>
@@ -2635,14 +2624,14 @@
         <v>12</v>
       </c>
       <c r="E22" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G22" s="7">
         <f t="shared" si="0"/>
-        <v>114000</v>
+        <v>132000</v>
       </c>
       <c r="H22" s="44" t="s">
         <v>273</v>
@@ -2657,7 +2646,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>10</v>
       </c>
@@ -2671,14 +2660,14 @@
         <v>3</v>
       </c>
       <c r="E23" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G23" s="7">
         <f t="shared" ref="G23" si="3">D23*E23</f>
-        <v>28500</v>
+        <v>33000</v>
       </c>
       <c r="H23" s="44" t="s">
         <v>273</v>
@@ -2693,7 +2682,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>10</v>
       </c>
@@ -2707,14 +2696,14 @@
         <v>2</v>
       </c>
       <c r="E24" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G24" s="7">
         <f t="shared" si="0"/>
-        <v>19000</v>
+        <v>22000</v>
       </c>
       <c r="H24" s="44" t="s">
         <v>273</v>
@@ -2729,7 +2718,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>10</v>
       </c>
@@ -2743,14 +2732,14 @@
         <v>12</v>
       </c>
       <c r="E25" s="7">
-        <v>27000</v>
+        <v>27900</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>65</v>
       </c>
       <c r="G25" s="7">
         <f t="shared" si="0"/>
-        <v>324000</v>
+        <v>334800</v>
       </c>
       <c r="H25" s="44" t="s">
         <v>273</v>
@@ -2765,7 +2754,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>10</v>
       </c>
@@ -2779,14 +2768,14 @@
         <v>13</v>
       </c>
       <c r="E26" s="7">
-        <v>12900</v>
+        <v>15000</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G26" s="7">
         <f t="shared" si="0"/>
-        <v>167700</v>
+        <v>195000</v>
       </c>
       <c r="H26" s="44" t="s">
         <v>273</v>
@@ -2798,7 +2787,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>10</v>
       </c>
@@ -2812,14 +2801,14 @@
         <v>9</v>
       </c>
       <c r="E27" s="7">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G27" s="7">
         <f t="shared" si="0"/>
-        <v>108000</v>
+        <v>126000</v>
       </c>
       <c r="H27" s="44" t="s">
         <v>273</v>
@@ -2834,7 +2823,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>10</v>
       </c>
@@ -2870,7 +2859,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>10</v>
       </c>
@@ -2906,7 +2895,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="20" t="s">
         <v>82</v>
       </c>
@@ -2942,7 +2931,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
         <v>82</v>
       </c>
@@ -2975,7 +2964,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
         <v>82</v>
       </c>
@@ -3008,7 +2997,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
         <v>82</v>
       </c>
@@ -3044,7 +3033,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="20" t="s">
         <v>82</v>
       </c>
@@ -3080,7 +3069,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
         <v>82</v>
       </c>
@@ -3094,14 +3083,14 @@
         <v>23</v>
       </c>
       <c r="E35" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G35" s="7">
         <f t="shared" si="0"/>
-        <v>218500</v>
+        <v>253000</v>
       </c>
       <c r="H35" s="13" t="s">
         <v>182</v>
@@ -3113,7 +3102,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="20" t="s">
         <v>82</v>
       </c>
@@ -3127,14 +3116,14 @@
         <v>12</v>
       </c>
       <c r="E36" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G36" s="7">
         <f t="shared" si="0"/>
-        <v>114000</v>
+        <v>132000</v>
       </c>
       <c r="H36" s="13" t="s">
         <v>182</v>
@@ -3146,7 +3135,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="20" t="s">
         <v>82</v>
       </c>
@@ -3160,14 +3149,14 @@
         <v>8</v>
       </c>
       <c r="E37" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G37" s="7">
         <f t="shared" si="0"/>
-        <v>76000</v>
+        <v>88000</v>
       </c>
       <c r="H37" s="13" t="s">
         <v>182</v>
@@ -3182,7 +3171,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
         <v>82</v>
       </c>
@@ -3196,14 +3185,14 @@
         <v>11</v>
       </c>
       <c r="E38" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G38" s="7">
         <f>D38*E38</f>
-        <v>104500</v>
+        <v>121000</v>
       </c>
       <c r="H38" s="13" t="s">
         <v>182</v>
@@ -3218,7 +3207,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="20" t="s">
         <v>82</v>
       </c>
@@ -3232,14 +3221,14 @@
         <v>3</v>
       </c>
       <c r="E39" s="7">
-        <v>17900</v>
+        <v>21000</v>
       </c>
       <c r="F39" s="28" t="s">
         <v>210</v>
       </c>
       <c r="G39" s="7">
         <f>D39*E39</f>
-        <v>53700</v>
+        <v>63000</v>
       </c>
       <c r="H39" s="13" t="s">
         <v>182</v>
@@ -3254,7 +3243,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="20" t="s">
         <v>82</v>
       </c>
@@ -3268,14 +3257,14 @@
         <v>12</v>
       </c>
       <c r="E40" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G40" s="7">
         <f>D40*E40</f>
-        <v>126000</v>
+        <v>144000</v>
       </c>
       <c r="H40" s="13" t="s">
         <v>182</v>
@@ -3290,7 +3279,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="20" t="s">
         <v>82</v>
       </c>
@@ -3304,14 +3293,14 @@
         <v>16</v>
       </c>
       <c r="E41" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G41" s="7">
         <f>D41*E41</f>
-        <v>168000</v>
+        <v>192000</v>
       </c>
       <c r="H41" s="13" t="s">
         <v>182</v>
@@ -3326,7 +3315,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="20" t="s">
         <v>82</v>
       </c>
@@ -3340,14 +3329,14 @@
         <v>2</v>
       </c>
       <c r="E42" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G42" s="7">
         <f t="shared" si="0"/>
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="H42" s="13" t="s">
         <v>182</v>
@@ -3362,7 +3351,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="20" t="s">
         <v>82</v>
       </c>
@@ -3376,14 +3365,14 @@
         <v>3</v>
       </c>
       <c r="E43" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G43" s="7">
         <f>D43*E43</f>
-        <v>31500</v>
+        <v>36000</v>
       </c>
       <c r="H43" s="13" t="s">
         <v>182</v>
@@ -3398,7 +3387,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="20" t="s">
         <v>82</v>
       </c>
@@ -3412,14 +3401,14 @@
         <v>3</v>
       </c>
       <c r="E44" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G44" s="7">
         <f t="shared" si="0"/>
-        <v>31500</v>
+        <v>36000</v>
       </c>
       <c r="H44" s="13" t="s">
         <v>182</v>
@@ -3434,7 +3423,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="20" t="s">
         <v>82</v>
       </c>
@@ -3448,14 +3437,14 @@
         <v>3</v>
       </c>
       <c r="E45" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G45" s="7">
         <f t="shared" si="0"/>
-        <v>31500</v>
+        <v>36000</v>
       </c>
       <c r="H45" s="13" t="s">
         <v>182</v>
@@ -3470,7 +3459,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="20" t="s">
         <v>82</v>
       </c>
@@ -3484,14 +3473,14 @@
         <v>13</v>
       </c>
       <c r="E46" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G46" s="7">
         <f t="shared" si="0"/>
-        <v>136500</v>
+        <v>156000</v>
       </c>
       <c r="H46" s="13" t="s">
         <v>182</v>
@@ -3503,7 +3492,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="20" t="s">
         <v>82</v>
       </c>
@@ -3517,14 +3506,14 @@
         <v>8</v>
       </c>
       <c r="E47" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G47" s="7">
         <f t="shared" si="0"/>
-        <v>84000</v>
+        <v>96000</v>
       </c>
       <c r="H47" s="13" t="s">
         <v>182</v>
@@ -3536,7 +3525,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="20" t="s">
         <v>82</v>
       </c>
@@ -3550,14 +3539,14 @@
         <v>4</v>
       </c>
       <c r="E48" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G48" s="7">
         <f t="shared" ref="G48" si="4">D48*E48</f>
-        <v>42000</v>
+        <v>48000</v>
       </c>
       <c r="H48" s="13" t="s">
         <v>182</v>
@@ -3569,7 +3558,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="20" t="s">
         <v>82</v>
       </c>
@@ -3583,14 +3572,14 @@
         <v>3</v>
       </c>
       <c r="E49" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G49" s="7">
         <f t="shared" si="0"/>
-        <v>31500</v>
+        <v>36000</v>
       </c>
       <c r="H49" s="13" t="s">
         <v>182</v>
@@ -3602,7 +3591,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="20" t="s">
         <v>82</v>
       </c>
@@ -3616,14 +3605,14 @@
         <v>3</v>
       </c>
       <c r="E50" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G50" s="7">
         <f t="shared" si="0"/>
-        <v>31500</v>
+        <v>36000</v>
       </c>
       <c r="H50" s="13" t="s">
         <v>182</v>
@@ -3635,7 +3624,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="20" t="s">
         <v>82</v>
       </c>
@@ -3649,14 +3638,14 @@
         <v>3</v>
       </c>
       <c r="E51" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G51" s="7">
         <f t="shared" si="0"/>
-        <v>31500</v>
+        <v>36000</v>
       </c>
       <c r="H51" s="13" t="s">
         <v>182</v>
@@ -3668,7 +3657,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="20" t="s">
         <v>82</v>
       </c>
@@ -3682,14 +3671,14 @@
         <v>3</v>
       </c>
       <c r="E52" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G52" s="7">
         <f t="shared" si="0"/>
-        <v>31500</v>
+        <v>36000</v>
       </c>
       <c r="H52" s="13" t="s">
         <v>182</v>
@@ -3701,7 +3690,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="20" t="s">
         <v>82</v>
       </c>
@@ -3715,14 +3704,14 @@
         <v>2</v>
       </c>
       <c r="E53" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G53" s="7">
         <f t="shared" ref="G53" si="5">D53*E53</f>
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="H53" s="13" t="s">
         <v>182</v>
@@ -3734,7 +3723,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="20" t="s">
         <v>82</v>
       </c>
@@ -3748,14 +3737,14 @@
         <v>3</v>
       </c>
       <c r="E54" s="7">
-        <v>8300</v>
+        <v>10500</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G54" s="7">
         <f>D54*E54</f>
-        <v>24900</v>
+        <v>31500</v>
       </c>
       <c r="H54" s="13" t="s">
         <v>182</v>
@@ -3770,7 +3759,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="20" t="s">
         <v>82</v>
       </c>
@@ -3784,14 +3773,14 @@
         <v>4</v>
       </c>
       <c r="E55" s="7">
-        <v>17700</v>
+        <v>19900</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G55" s="7">
         <f t="shared" si="0"/>
-        <v>70800</v>
+        <v>79600</v>
       </c>
       <c r="H55" s="13" t="s">
         <v>182</v>
@@ -3806,7 +3795,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="20" t="s">
         <v>82</v>
       </c>
@@ -3820,14 +3809,14 @@
         <v>2</v>
       </c>
       <c r="E56" s="7">
-        <v>18900</v>
+        <v>19900</v>
       </c>
       <c r="F56" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G56" s="7">
         <f>D56*E56</f>
-        <v>37800</v>
+        <v>39800</v>
       </c>
       <c r="H56" s="13" t="s">
         <v>182</v>
@@ -3842,7 +3831,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="20" t="s">
         <v>82</v>
       </c>
@@ -3856,14 +3845,14 @@
         <v>5</v>
       </c>
       <c r="E57" s="7">
-        <v>18800</v>
+        <v>19900</v>
       </c>
       <c r="F57" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G57" s="7">
         <f t="shared" si="0"/>
-        <v>94000</v>
+        <v>99500</v>
       </c>
       <c r="H57" s="13" t="s">
         <v>182</v>
@@ -3878,7 +3867,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="20" t="s">
         <v>82</v>
       </c>
@@ -3914,7 +3903,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="20" t="s">
         <v>82</v>
       </c>
@@ -3928,14 +3917,14 @@
         <v>3</v>
       </c>
       <c r="E59" s="7">
-        <v>18900</v>
+        <v>29000</v>
       </c>
       <c r="F59" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G59" s="7">
         <f>D59*E59</f>
-        <v>56700</v>
+        <v>87000</v>
       </c>
       <c r="H59" s="13" t="s">
         <v>182</v>
@@ -3950,7 +3939,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="20" t="s">
         <v>82</v>
       </c>
@@ -3964,14 +3953,14 @@
         <v>3</v>
       </c>
       <c r="E60" s="7">
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="F60" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G60" s="7">
         <f t="shared" si="0"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="H60" s="13" t="s">
         <v>182</v>
@@ -3986,7 +3975,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="20" t="s">
         <v>82</v>
       </c>
@@ -4000,14 +3989,14 @@
         <v>5</v>
       </c>
       <c r="E61" s="7">
-        <v>11900</v>
+        <v>14900</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G61" s="7">
         <f t="shared" si="0"/>
-        <v>59500</v>
+        <v>74500</v>
       </c>
       <c r="H61" s="13" t="s">
         <v>182</v>
@@ -4022,7 +4011,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="20" t="s">
         <v>82</v>
       </c>
@@ -4036,14 +4025,14 @@
         <v>3</v>
       </c>
       <c r="E62" s="7">
-        <v>11900</v>
+        <v>14900</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G62" s="7">
         <f t="shared" si="0"/>
-        <v>35700</v>
+        <v>44700</v>
       </c>
       <c r="H62" s="13" t="s">
         <v>182</v>
@@ -4055,7 +4044,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="20" t="s">
         <v>82</v>
       </c>
@@ -4091,7 +4080,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="20" t="s">
         <v>82</v>
       </c>
@@ -4124,7 +4113,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="25" t="s">
         <v>154</v>
       </c>
@@ -4157,7 +4146,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="25" t="s">
         <v>154</v>
       </c>
@@ -4190,7 +4179,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="25" t="s">
         <v>154</v>
       </c>
@@ -4223,7 +4212,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="25" t="s">
         <v>154</v>
       </c>
@@ -4237,14 +4226,14 @@
         <v>12</v>
       </c>
       <c r="E68" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G68" s="7">
         <f t="shared" si="0"/>
-        <v>114000</v>
+        <v>132000</v>
       </c>
       <c r="H68" s="13" t="s">
         <v>182</v>
@@ -4256,7 +4245,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="25" t="s">
         <v>154</v>
       </c>
@@ -4289,7 +4278,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="25" t="s">
         <v>154</v>
       </c>
@@ -4303,14 +4292,14 @@
         <v>6</v>
       </c>
       <c r="E70" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G70" s="7">
         <f t="shared" si="0"/>
-        <v>57000</v>
+        <v>66000</v>
       </c>
       <c r="H70" s="44" t="s">
         <v>273</v>
@@ -4322,7 +4311,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="25" t="s">
         <v>154</v>
       </c>
@@ -4336,14 +4325,14 @@
         <v>4</v>
       </c>
       <c r="E71" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G71" s="7">
         <f t="shared" si="0"/>
-        <v>38000</v>
+        <v>44000</v>
       </c>
       <c r="H71" s="44" t="s">
         <v>273</v>
@@ -4355,7 +4344,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="25" t="s">
         <v>154</v>
       </c>
@@ -4369,14 +4358,14 @@
         <v>5</v>
       </c>
       <c r="E72" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G72" s="7">
         <f t="shared" si="0"/>
-        <v>47500</v>
+        <v>55000</v>
       </c>
       <c r="H72" s="44" t="s">
         <v>273</v>
@@ -4388,7 +4377,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="25" t="s">
         <v>154</v>
       </c>
@@ -4402,14 +4391,14 @@
         <v>1</v>
       </c>
       <c r="E73" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G73" s="7">
         <f t="shared" si="0"/>
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="H73" s="44" t="s">
         <v>273</v>
@@ -4421,7 +4410,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="25" t="s">
         <v>154</v>
       </c>
@@ -4435,14 +4424,14 @@
         <v>1</v>
       </c>
       <c r="E74" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G74" s="7">
         <f t="shared" si="0"/>
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="H74" s="44" t="s">
         <v>273</v>
@@ -4454,7 +4443,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="25" t="s">
         <v>154</v>
       </c>
@@ -4468,14 +4457,14 @@
         <v>5</v>
       </c>
       <c r="E75" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G75" s="7">
         <f t="shared" si="0"/>
-        <v>52500</v>
+        <v>60000</v>
       </c>
       <c r="H75" s="13" t="s">
         <v>182</v>
@@ -4487,7 +4476,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="25" t="s">
         <v>154</v>
       </c>
@@ -4501,14 +4490,14 @@
         <v>1</v>
       </c>
       <c r="E76" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G76" s="7">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="H76" s="44" t="s">
         <v>273</v>
@@ -4523,7 +4512,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="26" t="s">
         <v>179</v>
       </c>
@@ -4537,14 +4526,14 @@
         <v>1</v>
       </c>
       <c r="E77" s="7">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="F77" s="27" t="s">
         <v>13</v>
       </c>
       <c r="G77" s="7">
         <f t="shared" si="0"/>
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="H77" s="13" t="s">
         <v>182</v>
@@ -4556,7 +4545,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="26" t="s">
         <v>179</v>
       </c>
@@ -4570,14 +4559,14 @@
         <v>1</v>
       </c>
       <c r="E78" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G78" s="7">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="H78" s="13" t="s">
         <v>182</v>
@@ -4589,7 +4578,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="26" t="s">
         <v>179</v>
       </c>
@@ -4603,14 +4592,14 @@
         <v>1</v>
       </c>
       <c r="E79" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G79" s="7">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="H79" s="13" t="s">
         <v>182</v>
@@ -4622,7 +4611,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="26" t="s">
         <v>179</v>
       </c>
@@ -4636,14 +4625,14 @@
         <v>1</v>
       </c>
       <c r="E80" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G80" s="7">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="H80" s="13" t="s">
         <v>182</v>
@@ -4655,7 +4644,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="26" t="s">
         <v>179</v>
       </c>
@@ -4669,14 +4658,14 @@
         <v>1</v>
       </c>
       <c r="E81" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G81" s="7">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="H81" s="13" t="s">
         <v>182</v>
@@ -4688,7 +4677,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="26" t="s">
         <v>179</v>
       </c>
@@ -4702,14 +4691,14 @@
         <v>1</v>
       </c>
       <c r="E82" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G82" s="7">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="H82" s="13" t="s">
         <v>182</v>
@@ -4721,7 +4710,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="26" t="s">
         <v>179</v>
       </c>
@@ -4735,14 +4724,14 @@
         <v>1</v>
       </c>
       <c r="E83" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G83" s="7">
         <f t="shared" ref="G83" si="6">D83*E83</f>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="H83" s="13" t="s">
         <v>182</v>
@@ -4754,7 +4743,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="26" t="s">
         <v>179</v>
       </c>
@@ -4768,14 +4757,14 @@
         <v>1</v>
       </c>
       <c r="E84" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G84" s="7">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="H84" s="13" t="s">
         <v>182</v>
@@ -4787,7 +4776,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="26" t="s">
         <v>179</v>
       </c>
@@ -4801,14 +4790,14 @@
         <v>1</v>
       </c>
       <c r="E85" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G85" s="7">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="H85" s="13" t="s">
         <v>182</v>
@@ -4820,7 +4809,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="26" t="s">
         <v>179</v>
       </c>
@@ -4834,14 +4823,14 @@
         <v>1</v>
       </c>
       <c r="E86" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G86" s="7">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="H86" s="13" t="s">
         <v>182</v>
@@ -4856,7 +4845,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="26" t="s">
         <v>179</v>
       </c>
@@ -4870,14 +4859,14 @@
         <v>1</v>
       </c>
       <c r="E87" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G87" s="7">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="H87" s="13" t="s">
         <v>182</v>
@@ -4892,7 +4881,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="26" t="s">
         <v>179</v>
       </c>
@@ -4906,14 +4895,14 @@
         <v>1</v>
       </c>
       <c r="E88" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G88" s="7">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="H88" s="13" t="s">
         <v>182</v>
@@ -4928,7 +4917,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="26" t="s">
         <v>179</v>
       </c>
@@ -4942,14 +4931,14 @@
         <v>1</v>
       </c>
       <c r="E89" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G89" s="7">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="H89" s="13" t="s">
         <v>182</v>
@@ -4964,7 +4953,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="26" t="s">
         <v>179</v>
       </c>
@@ -4978,14 +4967,14 @@
         <v>1</v>
       </c>
       <c r="E90" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G90" s="7">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="H90" s="13" t="s">
         <v>182</v>
@@ -5000,7 +4989,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="26" t="s">
         <v>179</v>
       </c>
@@ -5014,14 +5003,14 @@
         <v>1</v>
       </c>
       <c r="E91" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G91" s="7">
         <f>D91*E91</f>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="H91" s="13" t="s">
         <v>182</v>
@@ -5036,7 +5025,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="26" t="s">
         <v>179</v>
       </c>
@@ -5050,14 +5039,14 @@
         <v>1</v>
       </c>
       <c r="E92" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G92" s="7">
         <f>D92*E92</f>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="H92" s="13" t="s">
         <v>182</v>
@@ -5072,7 +5061,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="26" t="s">
         <v>179</v>
       </c>
@@ -5086,14 +5075,14 @@
         <v>1</v>
       </c>
       <c r="E93" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G93" s="7">
         <f>D93*E93</f>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="H93" s="13" t="s">
         <v>182</v>
@@ -5108,7 +5097,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="26" t="s">
         <v>179</v>
       </c>
@@ -5122,14 +5111,14 @@
         <v>1</v>
       </c>
       <c r="E94" s="7">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G94" s="7">
         <f t="shared" ref="G94" si="7">D94*E94</f>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="H94" s="13" t="s">
         <v>182</v>
@@ -5144,7 +5133,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="26" t="s">
         <v>179</v>
       </c>
@@ -5158,14 +5147,14 @@
         <v>1</v>
       </c>
       <c r="E95" s="7">
-        <v>18900</v>
+        <v>22000</v>
       </c>
       <c r="F95" s="28" t="s">
         <v>210</v>
       </c>
       <c r="G95" s="7">
         <f>D95*E95</f>
-        <v>18900</v>
+        <v>22000</v>
       </c>
       <c r="H95" s="13" t="s">
         <v>182</v>
@@ -5180,7 +5169,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="26" t="s">
         <v>179</v>
       </c>
@@ -5194,14 +5183,14 @@
         <v>1</v>
       </c>
       <c r="E96" s="7">
-        <v>23500</v>
+        <v>29000</v>
       </c>
       <c r="F96" s="28" t="s">
         <v>210</v>
       </c>
       <c r="G96" s="7">
         <f>D96*E96</f>
-        <v>23500</v>
+        <v>29000</v>
       </c>
       <c r="H96" s="13" t="s">
         <v>182</v>
@@ -5216,7 +5205,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="26" t="s">
         <v>179</v>
       </c>
@@ -5230,14 +5219,14 @@
         <v>1</v>
       </c>
       <c r="E97" s="7">
-        <v>17900</v>
+        <v>21000</v>
       </c>
       <c r="F97" s="28" t="s">
         <v>210</v>
       </c>
       <c r="G97" s="7">
         <f>D97*E97</f>
-        <v>17900</v>
+        <v>21000</v>
       </c>
       <c r="H97" s="13" t="s">
         <v>182</v>
@@ -5249,7 +5238,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="26" t="s">
         <v>179</v>
       </c>
@@ -5263,14 +5252,14 @@
         <v>1</v>
       </c>
       <c r="E98" s="7">
-        <v>18900</v>
+        <v>22000</v>
       </c>
       <c r="F98" s="28" t="s">
         <v>210</v>
       </c>
       <c r="G98" s="7">
         <f t="shared" ref="G98" si="8">D98*E98</f>
-        <v>18900</v>
+        <v>22000</v>
       </c>
       <c r="H98" s="13" t="s">
         <v>182</v>
@@ -5282,7 +5271,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="26" t="s">
         <v>179</v>
       </c>
@@ -5296,14 +5285,14 @@
         <v>1</v>
       </c>
       <c r="E99" s="7">
-        <v>17900</v>
+        <v>21000</v>
       </c>
       <c r="F99" s="28" t="s">
         <v>210</v>
       </c>
       <c r="G99" s="7">
         <f>D99*E99</f>
-        <v>17900</v>
+        <v>21000</v>
       </c>
       <c r="H99" s="13" t="s">
         <v>182</v>
@@ -5315,7 +5304,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="26" t="s">
         <v>179</v>
       </c>
@@ -5329,14 +5318,14 @@
         <v>1</v>
       </c>
       <c r="E100" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G100" s="7">
         <f>D100*E100</f>
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="H100" s="13" t="s">
         <v>182</v>
@@ -5348,7 +5337,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="26" t="s">
         <v>179</v>
       </c>
@@ -5362,14 +5351,14 @@
         <v>1</v>
       </c>
       <c r="E101" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G101" s="7">
         <f t="shared" si="0"/>
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="H101" s="13" t="s">
         <v>182</v>
@@ -5381,7 +5370,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="26" t="s">
         <v>179</v>
       </c>
@@ -5395,14 +5384,14 @@
         <v>1</v>
       </c>
       <c r="E102" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G102" s="7">
         <f t="shared" si="0"/>
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="H102" s="13" t="s">
         <v>182</v>
@@ -5414,7 +5403,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="26" t="s">
         <v>179</v>
       </c>
@@ -5428,14 +5417,14 @@
         <v>1</v>
       </c>
       <c r="E103" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G103" s="7">
         <f t="shared" si="0"/>
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="H103" s="13" t="s">
         <v>182</v>
@@ -5450,7 +5439,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="26" t="s">
         <v>179</v>
       </c>
@@ -5464,14 +5453,14 @@
         <v>1</v>
       </c>
       <c r="E104" s="7">
-        <v>12500</v>
+        <v>14500</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G104" s="7">
         <f>D104*E104</f>
-        <v>12500</v>
+        <v>14500</v>
       </c>
       <c r="H104" s="13" t="s">
         <v>182</v>
@@ -5486,7 +5475,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="26" t="s">
         <v>179</v>
       </c>
@@ -5500,14 +5489,14 @@
         <v>1</v>
       </c>
       <c r="E105" s="7">
-        <v>13500</v>
+        <v>16000</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G105" s="7">
         <f>D105*E105</f>
-        <v>13500</v>
+        <v>16000</v>
       </c>
       <c r="H105" s="13" t="s">
         <v>182</v>
@@ -5522,7 +5511,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="26" t="s">
         <v>179</v>
       </c>
@@ -5555,7 +5544,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="26" t="s">
         <v>179</v>
       </c>
@@ -5569,14 +5558,14 @@
         <v>1</v>
       </c>
       <c r="E107" s="7">
-        <v>8900</v>
+        <v>11000</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G107" s="7">
         <f t="shared" si="0"/>
-        <v>8900</v>
+        <v>11000</v>
       </c>
       <c r="H107" s="13" t="s">
         <v>182</v>
@@ -5591,7 +5580,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="26" t="s">
         <v>179</v>
       </c>
@@ -5605,14 +5594,14 @@
         <v>1</v>
       </c>
       <c r="E108" s="7">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G108" s="7">
         <f t="shared" si="0"/>
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="H108" s="13" t="s">
         <v>182</v>
@@ -5624,7 +5613,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="26" t="s">
         <v>179</v>
       </c>
@@ -5638,14 +5627,14 @@
         <v>1</v>
       </c>
       <c r="E109" s="7">
-        <v>12500</v>
+        <v>14500</v>
       </c>
       <c r="F109" s="29" t="s">
         <v>46</v>
       </c>
       <c r="G109" s="7">
         <f t="shared" si="0"/>
-        <v>12500</v>
+        <v>14500</v>
       </c>
       <c r="H109" s="13" t="s">
         <v>182</v>
@@ -5660,7 +5649,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="26" t="s">
         <v>179</v>
       </c>
@@ -5674,14 +5663,14 @@
         <v>1</v>
       </c>
       <c r="E110" s="7">
-        <v>15900</v>
+        <v>18500</v>
       </c>
       <c r="F110" s="30" t="s">
         <v>226</v>
       </c>
       <c r="G110" s="7">
         <f t="shared" si="0"/>
-        <v>15900</v>
+        <v>18500</v>
       </c>
       <c r="H110" s="13" t="s">
         <v>182</v>
@@ -5696,7 +5685,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="26" t="s">
         <v>179</v>
       </c>
@@ -5710,14 +5699,14 @@
         <v>1</v>
       </c>
       <c r="E111" s="7">
-        <v>15900</v>
+        <v>18500</v>
       </c>
       <c r="F111" s="30" t="s">
         <v>226</v>
       </c>
       <c r="G111" s="7">
         <f t="shared" si="0"/>
-        <v>15900</v>
+        <v>18500</v>
       </c>
       <c r="H111" s="13" t="s">
         <v>182</v>
@@ -5732,7 +5721,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="26" t="s">
         <v>179</v>
       </c>
@@ -5746,14 +5735,14 @@
         <v>1</v>
       </c>
       <c r="E112" s="7">
-        <v>25500</v>
+        <v>29500</v>
       </c>
       <c r="F112" s="31" t="s">
         <v>33</v>
       </c>
       <c r="G112" s="7">
         <f>D112*E112</f>
-        <v>25500</v>
+        <v>29500</v>
       </c>
       <c r="H112" s="13" t="s">
         <v>182</v>
@@ -5768,7 +5757,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="26" t="s">
         <v>179</v>
       </c>
@@ -5782,14 +5771,14 @@
         <v>1</v>
       </c>
       <c r="E113" s="7">
-        <v>25500</v>
+        <v>29500</v>
       </c>
       <c r="F113" s="31" t="s">
         <v>33</v>
       </c>
       <c r="G113" s="7">
         <f t="shared" si="0"/>
-        <v>25500</v>
+        <v>29500</v>
       </c>
       <c r="H113" s="13" t="s">
         <v>182</v>
@@ -5804,7 +5793,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="26" t="s">
         <v>179</v>
       </c>
@@ -5818,14 +5807,14 @@
         <v>1</v>
       </c>
       <c r="E114" s="7">
-        <v>19900</v>
+        <v>23000</v>
       </c>
       <c r="F114" s="31" t="s">
         <v>33</v>
       </c>
       <c r="G114" s="7">
         <f>D114*E114</f>
-        <v>19900</v>
+        <v>23000</v>
       </c>
       <c r="H114" s="13" t="s">
         <v>182</v>
@@ -5837,7 +5826,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="26" t="s">
         <v>179</v>
       </c>
@@ -5851,14 +5840,14 @@
         <v>1</v>
       </c>
       <c r="E115" s="7">
-        <v>19900</v>
+        <v>23000</v>
       </c>
       <c r="F115" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G115" s="7">
         <f t="shared" si="0"/>
-        <v>19900</v>
+        <v>23000</v>
       </c>
       <c r="H115" s="13" t="s">
         <v>182</v>
@@ -5870,7 +5859,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="26" t="s">
         <v>179</v>
       </c>
@@ -5884,14 +5873,14 @@
         <v>1</v>
       </c>
       <c r="E116" s="7">
-        <v>19900</v>
+        <v>23000</v>
       </c>
       <c r="F116" s="17" t="s">
         <v>65</v>
       </c>
       <c r="G116" s="7">
         <f t="shared" si="0"/>
-        <v>19900</v>
+        <v>23000</v>
       </c>
       <c r="H116" s="13" t="s">
         <v>182</v>
@@ -5903,7 +5892,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="26" t="s">
         <v>179</v>
       </c>
@@ -5939,7 +5928,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="26" t="s">
         <v>179</v>
       </c>
@@ -5953,14 +5942,14 @@
         <v>1</v>
       </c>
       <c r="E118" s="7">
-        <v>11900</v>
+        <v>19900</v>
       </c>
       <c r="F118" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G118" s="7">
         <f t="shared" ref="G118" si="9">D118*E118</f>
-        <v>11900</v>
+        <v>19900</v>
       </c>
       <c r="H118" s="13" t="s">
         <v>182</v>
@@ -5975,7 +5964,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="26" t="s">
         <v>179</v>
       </c>
@@ -5989,14 +5978,14 @@
         <v>1</v>
       </c>
       <c r="E119" s="7">
-        <v>25100</v>
+        <v>22900</v>
       </c>
       <c r="F119" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G119" s="7">
         <f t="shared" si="0"/>
-        <v>25100</v>
+        <v>22900</v>
       </c>
       <c r="H119" s="13" t="s">
         <v>182</v>
@@ -6011,7 +6000,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="26" t="s">
         <v>179</v>
       </c>
@@ -6025,14 +6014,14 @@
         <v>1</v>
       </c>
       <c r="E120" s="7">
-        <v>19800</v>
+        <v>22900</v>
       </c>
       <c r="F120" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G120" s="7">
         <f t="shared" ref="G120" si="10">D120*E120</f>
-        <v>19800</v>
+        <v>22900</v>
       </c>
       <c r="H120" s="13" t="s">
         <v>182</v>
@@ -6047,7 +6036,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="26" t="s">
         <v>179</v>
       </c>
@@ -6061,14 +6050,14 @@
         <v>1</v>
       </c>
       <c r="E121" s="7">
-        <v>13000</v>
+        <v>18000</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G121" s="7">
         <f t="shared" si="0"/>
-        <v>13000</v>
+        <v>18000</v>
       </c>
       <c r="H121" s="13" t="s">
         <v>182</v>
@@ -6083,7 +6072,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="26" t="s">
         <v>179</v>
       </c>
@@ -6097,14 +6086,14 @@
         <v>1</v>
       </c>
       <c r="E122" s="7">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="F122" s="27" t="s">
         <v>13</v>
       </c>
       <c r="G122" s="7">
         <f t="shared" si="0"/>
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="H122" s="13" t="s">
         <v>182</v>
@@ -6119,7 +6108,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="26" t="s">
         <v>179</v>
       </c>
@@ -6133,14 +6122,14 @@
         <v>1</v>
       </c>
       <c r="E123" s="7">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G123" s="7">
         <f t="shared" si="0"/>
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="H123" s="13" t="s">
         <v>182</v>
@@ -6155,7 +6144,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="26" t="s">
         <v>179</v>
       </c>
@@ -6169,14 +6158,14 @@
         <v>1</v>
       </c>
       <c r="E124" s="7">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="F124" s="28" t="s">
         <v>210</v>
       </c>
       <c r="G124" s="7">
         <f t="shared" si="0"/>
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="H124" s="13" t="s">
         <v>182</v>
@@ -6191,7 +6180,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="26" t="s">
         <v>179</v>
       </c>
@@ -6205,14 +6194,14 @@
         <v>1</v>
       </c>
       <c r="E125" s="7">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G125" s="7">
         <f t="shared" si="0"/>
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="H125" s="13" t="s">
         <v>182</v>
@@ -6227,7 +6216,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="26" t="s">
         <v>179</v>
       </c>
@@ -6241,14 +6230,14 @@
         <v>1</v>
       </c>
       <c r="E126" s="7">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G126" s="7">
         <f t="shared" ref="G126" si="11">D126*E126</f>
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="H126" s="13" t="s">
         <v>182</v>
@@ -6263,7 +6252,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="26" t="s">
         <v>179</v>
       </c>
@@ -6277,14 +6266,14 @@
         <v>1</v>
       </c>
       <c r="E127" s="7">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G127" s="7">
         <f>D127*E127</f>
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="H127" s="13" t="s">
         <v>182</v>
@@ -6299,7 +6288,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="26" t="s">
         <v>179</v>
       </c>
@@ -6313,14 +6302,14 @@
         <v>1</v>
       </c>
       <c r="E128" s="7">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G128" s="7">
         <f>D128*E128</f>
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="H128" s="13" t="s">
         <v>182</v>
@@ -6332,7 +6321,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="26" t="s">
         <v>179</v>
       </c>
@@ -6346,14 +6335,14 @@
         <v>1</v>
       </c>
       <c r="E129" s="7">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G129" s="7">
         <f t="shared" si="0"/>
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="H129" s="13" t="s">
         <v>182</v>
@@ -6368,7 +6357,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="26" t="s">
         <v>179</v>
       </c>
@@ -6404,7 +6393,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="26" t="s">
         <v>179</v>
       </c>
@@ -6440,7 +6429,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="26" t="s">
         <v>179</v>
       </c>
@@ -6454,14 +6443,14 @@
         <v>1</v>
       </c>
       <c r="E132" s="7">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="F132" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G132" s="7">
         <f t="shared" ref="G132:G133" si="12">D132*E132</f>
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="H132" s="13" t="s">
         <v>182</v>
@@ -6476,7 +6465,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="26" t="s">
         <v>179</v>
       </c>
@@ -6512,7 +6501,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="26" t="s">
         <v>179</v>
       </c>
@@ -6548,7 +6537,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="26" t="s">
         <v>179</v>
       </c>
@@ -6562,14 +6551,14 @@
         <v>1</v>
       </c>
       <c r="E135" s="7">
-        <v>17000</v>
+        <v>21000</v>
       </c>
       <c r="F135" s="28" t="s">
         <v>210</v>
       </c>
       <c r="G135" s="7">
         <f t="shared" ref="G135" si="13">D135*E135</f>
-        <v>17000</v>
+        <v>21000</v>
       </c>
       <c r="H135" s="13" t="s">
         <v>182</v>
@@ -6581,7 +6570,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>0</v>
       </c>
@@ -6613,7 +6602,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="str">
         <f>"En curso = " &amp; COUNTA(A2:A29)</f>
         <v>En curso = 28</v>
@@ -6632,7 +6621,7 @@
       </c>
       <c r="E137" s="7">
         <f>SUM(E2:E135)</f>
-        <v>1773200</v>
+        <v>1985300</v>
       </c>
       <c r="F137" s="46" t="str">
         <f>"B6 = " &amp; COUNTA(F2:F12,F14:F34,F27,F30:F34,F40:F55,F61:F63,F65:F67,F75:F94,F117,F121:F123,F125:F129)</f>
@@ -6640,7 +6629,7 @@
       </c>
       <c r="G137" s="7">
         <f>SUM(G2:G135)</f>
-        <v>7364800</v>
+        <v>8109800</v>
       </c>
       <c r="H137" s="13" t="str">
         <f>"Finalizados = " &amp; COUNTA(H28:H28,H30:H64,H66:H69,H75,H77:H135)</f>
@@ -6655,7 +6644,7 @@
         <v>Series = 85</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="20" t="str">
         <f>"Completado = " &amp; COUNTA(A30:A64)</f>
         <v>Completado = 35</v>
@@ -6677,7 +6666,7 @@
         <v>C6 = 230</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="25" t="str">
         <f>"Droppeado = " &amp; COUNTA(A65:A76)</f>
         <v>Droppeado = 12</v>
@@ -6695,7 +6684,7 @@
         <v>A5 = 43</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="26" t="str">
         <f>"Tomo único = " &amp; COUNTA(A77:A135)</f>
         <v>Tomo único = 59</v>
@@ -6713,7 +6702,7 @@
         <v>B6x2 = 8</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B141" s="3" t="str">
         <f>"Ovni Press = " &amp; COUNTA(B27,B121:B124)</f>
         <v>Ovni Press = 5</v>
@@ -6727,7 +6716,7 @@
         <v>C6x2 = 2</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B142" s="36" t="str">
         <f>"Planeta Cómic = " &amp; COUNTA(B28:B28,B55:B57,B119)</f>
         <v>Planeta Cómic = 5</v>
@@ -6741,899 +6730,899 @@
         <v>A5 color = 15</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B143" s="24" t="str">
         <f>"Utopia = " &amp; COUNTA(B63:B64)</f>
         <v>Utopia = 2</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B144" s="21" t="str">
         <f>"Merci = " &amp; COUNTA(B58)</f>
         <v>Merci = 1</v>
       </c>
     </row>
-    <row r="145" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B145" s="32" t="str">
         <f>"Milky Way = " &amp; COUNTA(B117)</f>
         <v>Milky Way = 1</v>
       </c>
     </row>
-    <row r="146" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B146" s="37" t="str">
         <f>"Moztros = " &amp; COUNTA(B59,B135)</f>
         <v>Moztros = 2</v>
       </c>
     </row>
-    <row r="147" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B147" s="38" t="str">
         <f>"Random Comics = " &amp; COUNTA(B29)</f>
         <v>Random Comics = 1</v>
       </c>
     </row>
-    <row r="148" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B148" s="43" t="str">
         <f>"Hotel de las Ideas = " &amp; COUNTA(B134)</f>
         <v>Hotel de las Ideas = 1</v>
       </c>
     </row>
-    <row r="149" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B149" s="47" t="str">
         <f>"Kibook Ediciones = " &amp; COUNTA(B133)</f>
         <v>Kibook Ediciones = 1</v>
       </c>
     </row>
-    <row r="150" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="151" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="152" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="153" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="154" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="155" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="156" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="157" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="158" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="159" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="160" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="150" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="F2:F136">
     <cfRule type="cellIs" dxfId="12" priority="5" operator="equal">
@@ -7651,7 +7640,7 @@
       <formula>"A5"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F43 F15 F39">
+  <conditionalFormatting sqref="F15 F39 F43">
     <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"B6"</formula>
     </cfRule>
@@ -7679,7 +7668,7 @@
       <formula>"A5"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H6 H28 H66:H69 H75 H77:H136 H30:H64">
+  <conditionalFormatting sqref="H4:H6 H28 H30:H64 H66:H69 H75 H77:H136">
     <cfRule type="containsText" dxfId="0" priority="47" operator="containsText" text="En publicacion">
       <formula>NOT(ISERROR(SEARCH(("En publicacion"),(H4))))</formula>
     </cfRule>
